--- a/DATA/EVALUACIONES/Exp01-V3/predicciones.xlsx
+++ b/DATA/EVALUACIONES/Exp01-V3/predicciones.xlsx
@@ -445,7 +445,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1597734838724136</v>
+        <v>0.3237916231155396</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.1928341835737228</v>
+        <v>0.2677924931049347</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.2163203954696655</v>
+        <v>0.2437224835157394</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1776958405971527</v>
+        <v>0.2323774844408035</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.06875402480363846</v>
+        <v>0.2424047887325287</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03967888280749321</v>
+        <v>0.2514427900314331</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>0.09106223285198212</v>
+        <v>0.2413268983364105</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1842396706342697</v>
+        <v>0.2503493428230286</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>20</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2501926422119141</v>
+        <v>0.2559722661972046</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>21</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3030204772949219</v>
+        <v>0.2887355089187622</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4248752892017365</v>
+        <v>0.3500611484050751</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6158815622329712</v>
+        <v>0.4519896507263184</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>24</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5831764340400696</v>
+        <v>0.5116831660270691</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>25</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5484946966171265</v>
+        <v>0.5852989554405212</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>26</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3249465227127075</v>
+        <v>0.5481356382369995</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>27</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3304517865180969</v>
+        <v>0.5767381191253662</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>28</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2748939692974091</v>
+        <v>0.5690398812294006</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>29</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2392421960830688</v>
+        <v>0.5604131817817688</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>30</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2108533382415771</v>
+        <v>0.5226901769638062</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>31</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1666595935821533</v>
+        <v>0.4607342779636383</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>32</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1143109276890755</v>
+        <v>0.3850522041320801</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>33</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1102065443992615</v>
+        <v>0.3557864427566528</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="n">
-        <v>0.207962229847908</v>
+        <v>0.3854763507843018</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2748220264911652</v>
+        <v>0.4128228724002838</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>36</v>
       </c>
       <c r="B26" t="n">
-        <v>0.3024646937847137</v>
+        <v>0.4373765587806702</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>37</v>
       </c>
       <c r="B27" t="n">
-        <v>0.3379285633563995</v>
+        <v>0.4413903951644897</v>
       </c>
     </row>
     <row r="28">
@@ -653,7 +653,7 @@
         <v>38</v>
       </c>
       <c r="B28" t="n">
-        <v>0.2393165677785873</v>
+        <v>0.4193184077739716</v>
       </c>
     </row>
     <row r="29">
@@ -661,7 +661,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="n">
-        <v>0.2201878875494003</v>
+        <v>0.418179988861084</v>
       </c>
     </row>
     <row r="30">
@@ -669,7 +669,7 @@
         <v>40</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2375244945287704</v>
+        <v>0.4416469931602478</v>
       </c>
     </row>
     <row r="31">
@@ -677,7 +677,7 @@
         <v>41</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2089260071516037</v>
+        <v>0.4514544606208801</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>42</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1713809370994568</v>
+        <v>0.4375715255737305</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1157229244709015</v>
+        <v>0.3949216604232788</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>44</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0926961749792099</v>
+        <v>0.3854923248291016</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>45</v>
       </c>
       <c r="B35" t="n">
-        <v>0.07623648643493652</v>
+        <v>0.3794302046298981</v>
       </c>
     </row>
     <row r="36">
@@ -717,7 +717,7 @@
         <v>46</v>
       </c>
       <c r="B36" t="n">
-        <v>0.09595698863267899</v>
+        <v>0.3805859386920929</v>
       </c>
     </row>
     <row r="37">
@@ -725,7 +725,7 @@
         <v>47</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1541192084550858</v>
+        <v>0.4067511558532715</v>
       </c>
     </row>
     <row r="38">
@@ -733,7 +733,7 @@
         <v>48</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1114738583564758</v>
+        <v>0.3893450498580933</v>
       </c>
     </row>
     <row r="39">
@@ -741,7 +741,7 @@
         <v>49</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1992723792791367</v>
+        <v>0.3998166024684906</v>
       </c>
     </row>
     <row r="40">
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="B40" t="n">
-        <v>0.223593607544899</v>
+        <v>0.3943124115467072</v>
       </c>
     </row>
     <row r="41">
@@ -757,7 +757,7 @@
         <v>51</v>
       </c>
       <c r="B41" t="n">
-        <v>0.2759524285793304</v>
+        <v>0.4104117155075073</v>
       </c>
     </row>
     <row r="42">
@@ -765,7 +765,7 @@
         <v>52</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2919606864452362</v>
+        <v>0.4197387993335724</v>
       </c>
     </row>
     <row r="43">
@@ -773,7 +773,7 @@
         <v>53</v>
       </c>
       <c r="B43" t="n">
-        <v>0.3192204535007477</v>
+        <v>0.4260765612125397</v>
       </c>
     </row>
     <row r="44">
@@ -781,7 +781,7 @@
         <v>54</v>
       </c>
       <c r="B44" t="n">
-        <v>0.280091792345047</v>
+        <v>0.3930408656597137</v>
       </c>
     </row>
     <row r="45">
@@ -789,7 +789,7 @@
         <v>55</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2374150156974792</v>
+        <v>0.3576927483081818</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>56</v>
       </c>
       <c r="B46" t="n">
-        <v>0.189245879650116</v>
+        <v>0.332371324300766</v>
       </c>
     </row>
     <row r="47">
@@ -805,7 +805,7 @@
         <v>57</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2219517379999161</v>
+        <v>0.3431078493595123</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>58</v>
       </c>
       <c r="B48" t="n">
-        <v>0.2955442368984222</v>
+        <v>0.3884095847606659</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>59</v>
       </c>
       <c r="B49" t="n">
-        <v>0.3957050740718842</v>
+        <v>0.4524601697921753</v>
       </c>
     </row>
     <row r="50">
@@ -829,7 +829,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="n">
-        <v>0.3468527495861053</v>
+        <v>0.4743793606758118</v>
       </c>
     </row>
     <row r="51">
@@ -837,7 +837,7 @@
         <v>61</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2699132263660431</v>
+        <v>0.4315305948257446</v>
       </c>
     </row>
     <row r="52">
@@ -845,7 +845,7 @@
         <v>62</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2394150346517563</v>
+        <v>0.4105619192123413</v>
       </c>
     </row>
     <row r="53">
@@ -853,7 +853,7 @@
         <v>63</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3332504332065582</v>
+        <v>0.4326317608356476</v>
       </c>
     </row>
     <row r="54">
@@ -861,7 +861,7 @@
         <v>64</v>
       </c>
       <c r="B54" t="n">
-        <v>0.3701110184192657</v>
+        <v>0.4501526653766632</v>
       </c>
     </row>
     <row r="55">
@@ -869,7 +869,7 @@
         <v>65</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4423338174819946</v>
+        <v>0.4692234992980957</v>
       </c>
     </row>
     <row r="56">
@@ -877,7 +877,7 @@
         <v>66</v>
       </c>
       <c r="B56" t="n">
-        <v>0.4957309663295746</v>
+        <v>0.4634667336940765</v>
       </c>
     </row>
     <row r="57">
@@ -885,7 +885,7 @@
         <v>67</v>
       </c>
       <c r="B57" t="n">
-        <v>0.5049790740013123</v>
+        <v>0.4558014273643494</v>
       </c>
     </row>
     <row r="58">
@@ -893,7 +893,7 @@
         <v>68</v>
       </c>
       <c r="B58" t="n">
-        <v>0.4632175862789154</v>
+        <v>0.4221552908420563</v>
       </c>
     </row>
     <row r="59">
@@ -901,7 +901,7 @@
         <v>69</v>
       </c>
       <c r="B59" t="n">
-        <v>0.3782654404640198</v>
+        <v>0.3966363370418549</v>
       </c>
     </row>
     <row r="60">
@@ -909,7 +909,7 @@
         <v>70</v>
       </c>
       <c r="B60" t="n">
-        <v>0.3768163025379181</v>
+        <v>0.4137263298034668</v>
       </c>
     </row>
     <row r="61">
@@ -917,7 +917,7 @@
         <v>71</v>
       </c>
       <c r="B61" t="n">
-        <v>0.4422291219234467</v>
+        <v>0.4575406908988953</v>
       </c>
     </row>
     <row r="62">
@@ -925,7 +925,7 @@
         <v>72</v>
       </c>
       <c r="B62" t="n">
-        <v>0.382583886384964</v>
+        <v>0.4668324589729309</v>
       </c>
     </row>
     <row r="63">
@@ -933,7 +933,7 @@
         <v>73</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2674016356468201</v>
+        <v>0.4326739311218262</v>
       </c>
     </row>
     <row r="64">
@@ -941,7 +941,7 @@
         <v>74</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1872548311948776</v>
+        <v>0.4069342315196991</v>
       </c>
     </row>
     <row r="65">
@@ -949,7 +949,7 @@
         <v>75</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2343164533376694</v>
+        <v>0.4263637661933899</v>
       </c>
     </row>
     <row r="66">
@@ -957,7 +957,7 @@
         <v>76</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1854622513055801</v>
+        <v>0.4309507608413696</v>
       </c>
     </row>
     <row r="67">
@@ -965,7 +965,7 @@
         <v>77</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1295405924320221</v>
+        <v>0.4039159119129181</v>
       </c>
     </row>
     <row r="68">
@@ -973,7 +973,7 @@
         <v>78</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1154662594199181</v>
+        <v>0.3799137473106384</v>
       </c>
     </row>
     <row r="69">
@@ -981,7 +981,7 @@
         <v>79</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1173304095864296</v>
+        <v>0.3584010601043701</v>
       </c>
     </row>
     <row r="70">
@@ -989,7 +989,7 @@
         <v>80</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1391530781984329</v>
+        <v>0.3512780964374542</v>
       </c>
     </row>
     <row r="71">
@@ -997,7 +997,7 @@
         <v>81</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1195825859904289</v>
+        <v>0.3436993658542633</v>
       </c>
     </row>
     <row r="72">
@@ -1005,7 +1005,7 @@
         <v>82</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1178030446171761</v>
+        <v>0.3444463610649109</v>
       </c>
     </row>
     <row r="73">
@@ -1013,7 +1013,7 @@
         <v>83</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1478957831859589</v>
+        <v>0.3664609789848328</v>
       </c>
     </row>
     <row r="74">
@@ -1021,7 +1021,7 @@
         <v>84</v>
       </c>
       <c r="B74" t="n">
-        <v>0.176334872841835</v>
+        <v>0.3796038627624512</v>
       </c>
     </row>
     <row r="75">
@@ -1029,7 +1029,7 @@
         <v>85</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1906178742647171</v>
+        <v>0.3788959681987762</v>
       </c>
     </row>
     <row r="76">
@@ -1037,7 +1037,7 @@
         <v>86</v>
       </c>
       <c r="B76" t="n">
-        <v>0.2682612836360931</v>
+        <v>0.4023352861404419</v>
       </c>
     </row>
     <row r="77">
@@ -1045,7 +1045,7 @@
         <v>87</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3259551227092743</v>
+        <v>0.4378324151039124</v>
       </c>
     </row>
     <row r="78">
@@ -1053,7 +1053,7 @@
         <v>88</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3506639897823334</v>
+        <v>0.4624272286891937</v>
       </c>
     </row>
     <row r="79">
@@ -1061,7 +1061,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3055261671543121</v>
+        <v>0.4715588688850403</v>
       </c>
     </row>
     <row r="80">
@@ -1069,7 +1069,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3012023568153381</v>
+        <v>0.4770215153694153</v>
       </c>
     </row>
     <row r="81">
@@ -1077,7 +1077,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>0.2041875869035721</v>
+        <v>0.4288210272789001</v>
       </c>
     </row>
     <row r="82">
@@ -1085,7 +1085,7 @@
         <v>92</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1145514622330666</v>
+        <v>0.3925087451934814</v>
       </c>
     </row>
     <row r="83">
@@ -1093,7 +1093,7 @@
         <v>93</v>
       </c>
       <c r="B83" t="n">
-        <v>0.04249636456370354</v>
+        <v>0.3592204749584198</v>
       </c>
     </row>
     <row r="84">
@@ -1101,7 +1101,7 @@
         <v>94</v>
       </c>
       <c r="B84" t="n">
-        <v>0.02670003846287727</v>
+        <v>0.3823365271091461</v>
       </c>
     </row>
     <row r="85">
@@ -1109,7 +1109,7 @@
         <v>95</v>
       </c>
       <c r="B85" t="n">
-        <v>0.02520963922142982</v>
+        <v>0.412071168422699</v>
       </c>
     </row>
     <row r="86">
@@ -1117,7 +1117,7 @@
         <v>96</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.06399194896221161</v>
+        <v>0.3896322250366211</v>
       </c>
     </row>
     <row r="87">
@@ -1125,7 +1125,7 @@
         <v>97</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.05523723736405373</v>
+        <v>0.3922739624977112</v>
       </c>
     </row>
     <row r="88">
@@ -1133,7 +1133,7 @@
         <v>98</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.08141906559467316</v>
+        <v>0.3774843513965607</v>
       </c>
     </row>
     <row r="89">
@@ -1141,7 +1141,7 @@
         <v>99</v>
       </c>
       <c r="B89" t="n">
-        <v>0.001033320091664791</v>
+        <v>0.4126364588737488</v>
       </c>
     </row>
     <row r="90">
@@ -1149,7 +1149,7 @@
         <v>100</v>
       </c>
       <c r="B90" t="n">
-        <v>0.03114412724971771</v>
+        <v>0.4233315885066986</v>
       </c>
     </row>
     <row r="91">
@@ -1157,7 +1157,7 @@
         <v>101</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.01308089029043913</v>
+        <v>0.4081398546695709</v>
       </c>
     </row>
     <row r="92">
@@ -1165,7 +1165,7 @@
         <v>102</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.01460149232298136</v>
+        <v>0.4012872576713562</v>
       </c>
     </row>
     <row r="93">
@@ -1173,7 +1173,7 @@
         <v>103</v>
       </c>
       <c r="B93" t="n">
-        <v>0.01470252405852079</v>
+        <v>0.3848394453525543</v>
       </c>
     </row>
     <row r="94">
@@ -1181,7 +1181,7 @@
         <v>104</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.01004865486174822</v>
+        <v>0.3607045412063599</v>
       </c>
     </row>
     <row r="95">
@@ -1189,7 +1189,7 @@
         <v>105</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.007577900774776936</v>
+        <v>0.348025381565094</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>106</v>
       </c>
       <c r="B96" t="n">
-        <v>0.01449413876980543</v>
+        <v>0.3380471169948578</v>
       </c>
     </row>
     <row r="97">
@@ -1205,7 +1205,7 @@
         <v>107</v>
       </c>
       <c r="B97" t="n">
-        <v>0.04082653298974037</v>
+        <v>0.3354451060295105</v>
       </c>
     </row>
     <row r="98">
@@ -1213,7 +1213,7 @@
         <v>108</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01670534536242485</v>
+        <v>0.3320803046226501</v>
       </c>
     </row>
     <row r="99">
@@ -1221,7 +1221,7 @@
         <v>109</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.05313176289200783</v>
+        <v>0.2890182733535767</v>
       </c>
     </row>
     <row r="100">
@@ -1229,7 +1229,7 @@
         <v>110</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.08200068026781082</v>
+        <v>0.2742505073547363</v>
       </c>
     </row>
     <row r="101">
@@ -1237,7 +1237,7 @@
         <v>111</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.005630289204418659</v>
+        <v>0.2632394433021545</v>
       </c>
     </row>
     <row r="102">
@@ -1245,7 +1245,7 @@
         <v>112</v>
       </c>
       <c r="B102" t="n">
-        <v>0.07589811831712723</v>
+        <v>0.2577722668647766</v>
       </c>
     </row>
     <row r="103">
@@ -1253,7 +1253,7 @@
         <v>113</v>
       </c>
       <c r="B103" t="n">
-        <v>0.2101752310991287</v>
+        <v>0.276197612285614</v>
       </c>
     </row>
     <row r="104">
@@ -1261,7 +1261,7 @@
         <v>114</v>
       </c>
       <c r="B104" t="n">
-        <v>0.2651171684265137</v>
+        <v>0.2743274569511414</v>
       </c>
     </row>
     <row r="105">
@@ -1269,7 +1269,7 @@
         <v>115</v>
       </c>
       <c r="B105" t="n">
-        <v>0.2753039300441742</v>
+        <v>0.2687981128692627</v>
       </c>
     </row>
     <row r="106">
@@ -1277,7 +1277,7 @@
         <v>116</v>
       </c>
       <c r="B106" t="n">
-        <v>0.2793892621994019</v>
+        <v>0.2758436501026154</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>117</v>
       </c>
       <c r="B107" t="n">
-        <v>0.3110446035861969</v>
+        <v>0.2936371564865112</v>
       </c>
     </row>
     <row r="108">
@@ -1293,7 +1293,7 @@
         <v>118</v>
       </c>
       <c r="B108" t="n">
-        <v>0.3754624426364899</v>
+        <v>0.3436420261859894</v>
       </c>
     </row>
     <row r="109">
@@ -1301,7 +1301,7 @@
         <v>119</v>
       </c>
       <c r="B109" t="n">
-        <v>0.5948323011398315</v>
+        <v>0.4495051801204681</v>
       </c>
     </row>
     <row r="110">
@@ -1309,7 +1309,7 @@
         <v>120</v>
       </c>
       <c r="B110" t="n">
-        <v>0.7173691391944885</v>
+        <v>0.5369491577148438</v>
       </c>
     </row>
     <row r="111">
@@ -1317,7 +1317,7 @@
         <v>121</v>
       </c>
       <c r="B111" t="n">
-        <v>0.6431766748428345</v>
+        <v>0.5761688947677612</v>
       </c>
     </row>
     <row r="112">
@@ -1325,7 +1325,7 @@
         <v>122</v>
       </c>
       <c r="B112" t="n">
-        <v>0.7563771605491638</v>
+        <v>0.6668634414672852</v>
       </c>
     </row>
     <row r="113">
@@ -1333,7 +1333,7 @@
         <v>123</v>
       </c>
       <c r="B113" t="n">
-        <v>0.8026823401451111</v>
+        <v>0.7244279980659485</v>
       </c>
     </row>
     <row r="114">
@@ -1341,7 +1341,7 @@
         <v>124</v>
       </c>
       <c r="B114" t="n">
-        <v>0.828662097454071</v>
+        <v>0.777895450592041</v>
       </c>
     </row>
     <row r="115">
@@ -1349,7 +1349,7 @@
         <v>125</v>
       </c>
       <c r="B115" t="n">
-        <v>0.8965631723403931</v>
+        <v>0.8240283131599426</v>
       </c>
     </row>
     <row r="116">
@@ -1357,7 +1357,7 @@
         <v>126</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9609697461128235</v>
+        <v>0.8567413687705994</v>
       </c>
     </row>
     <row r="117">
@@ -1365,7 +1365,7 @@
         <v>127</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9214680790901184</v>
+        <v>0.8625582456588745</v>
       </c>
     </row>
     <row r="118">
@@ -1373,7 +1373,7 @@
         <v>128</v>
       </c>
       <c r="B118" t="n">
-        <v>0.8991956114768982</v>
+        <v>0.8751750588417053</v>
       </c>
     </row>
     <row r="119">
@@ -1381,7 +1381,7 @@
         <v>129</v>
       </c>
       <c r="B119" t="n">
-        <v>0.8820622563362122</v>
+        <v>0.8831644654273987</v>
       </c>
     </row>
     <row r="120">
@@ -1389,7 +1389,7 @@
         <v>130</v>
       </c>
       <c r="B120" t="n">
-        <v>0.9245166182518005</v>
+        <v>0.9010166525840759</v>
       </c>
     </row>
     <row r="121">
@@ -1397,7 +1397,7 @@
         <v>131</v>
       </c>
       <c r="B121" t="n">
-        <v>1.05154824256897</v>
+        <v>0.9147381186485291</v>
       </c>
     </row>
     <row r="122">
@@ -1405,7 +1405,7 @@
         <v>132</v>
       </c>
       <c r="B122" t="n">
-        <v>1.063650846481323</v>
+        <v>0.9167142510414124</v>
       </c>
     </row>
     <row r="123">
@@ -1413,7 +1413,7 @@
         <v>133</v>
       </c>
       <c r="B123" t="n">
-        <v>0.9355773329734802</v>
+        <v>0.9046111702919006</v>
       </c>
     </row>
     <row r="124">
@@ -1421,7 +1421,7 @@
         <v>134</v>
       </c>
       <c r="B124" t="n">
-        <v>0.8883456587791443</v>
+        <v>0.9010039567947388</v>
       </c>
     </row>
     <row r="125">
@@ -1429,7 +1429,7 @@
         <v>135</v>
       </c>
       <c r="B125" t="n">
-        <v>0.8594077229499817</v>
+        <v>0.9042763710021973</v>
       </c>
     </row>
     <row r="126">
@@ -1437,7 +1437,7 @@
         <v>136</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7871019244194031</v>
+        <v>0.9039204120635986</v>
       </c>
     </row>
     <row r="127">
@@ -1445,7 +1445,7 @@
         <v>137</v>
       </c>
       <c r="B127" t="n">
-        <v>0.6819023489952087</v>
+        <v>0.8904300928115845</v>
       </c>
     </row>
     <row r="128">
@@ -1453,7 +1453,7 @@
         <v>138</v>
       </c>
       <c r="B128" t="n">
-        <v>0.5568534731864929</v>
+        <v>0.8618620634078979</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>139</v>
       </c>
       <c r="B129" t="n">
-        <v>0.4059755504131317</v>
+        <v>0.810535192489624</v>
       </c>
     </row>
     <row r="130">
@@ -1469,7 +1469,7 @@
         <v>140</v>
       </c>
       <c r="B130" t="n">
-        <v>0.195878878235817</v>
+        <v>0.7107657194137573</v>
       </c>
     </row>
     <row r="131">
@@ -1477,7 +1477,7 @@
         <v>141</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.01130779553204775</v>
+        <v>0.5728313326835632</v>
       </c>
     </row>
     <row r="132">
@@ -1485,7 +1485,7 @@
         <v>142</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.09616114944219589</v>
+        <v>0.4963480830192566</v>
       </c>
     </row>
     <row r="133">
@@ -1493,7 +1493,7 @@
         <v>143</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.1648501008749008</v>
+        <v>0.4381527602672577</v>
       </c>
     </row>
     <row r="134">
@@ -1501,7 +1501,7 @@
         <v>144</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.2917845249176025</v>
+        <v>0.4009372591972351</v>
       </c>
     </row>
     <row r="135">
@@ -1509,7 +1509,7 @@
         <v>145</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.3452554941177368</v>
+        <v>0.3539396822452545</v>
       </c>
     </row>
     <row r="136">
@@ -1517,7 +1517,7 @@
         <v>146</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.4145314395427704</v>
+        <v>0.3281491994857788</v>
       </c>
     </row>
     <row r="137">
@@ -1525,7 +1525,7 @@
         <v>147</v>
       </c>
       <c r="B137" t="n">
-        <v>-0.3926767408847809</v>
+        <v>0.3167436420917511</v>
       </c>
     </row>
     <row r="138">
@@ -1533,7 +1533,7 @@
         <v>148</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.3240696787834167</v>
+        <v>0.3213386535644531</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>149</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.2195188999176025</v>
+        <v>0.3546838462352753</v>
       </c>
     </row>
     <row r="140">
@@ -1549,7 +1549,7 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.1087954342365265</v>
+        <v>0.3791269659996033</v>
       </c>
     </row>
     <row r="141">
@@ -1557,7 +1557,7 @@
         <v>151</v>
       </c>
       <c r="B141" t="n">
-        <v>0.04343130812048912</v>
+        <v>0.4146232903003693</v>
       </c>
     </row>
     <row r="142">
@@ -1565,7 +1565,7 @@
         <v>152</v>
       </c>
       <c r="B142" t="n">
-        <v>0.2115120142698288</v>
+        <v>0.436028003692627</v>
       </c>
     </row>
     <row r="143">
@@ -1573,7 +1573,7 @@
         <v>153</v>
       </c>
       <c r="B143" t="n">
-        <v>0.2835022211074829</v>
+        <v>0.477384477853775</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>154</v>
       </c>
       <c r="B144" t="n">
-        <v>0.3622481226921082</v>
+        <v>0.5147094130516052</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>155</v>
       </c>
       <c r="B145" t="n">
-        <v>0.4891690015792847</v>
+        <v>0.5562218427658081</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>156</v>
       </c>
       <c r="B146" t="n">
-        <v>0.4372994005680084</v>
+        <v>0.5486596822738647</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>157</v>
       </c>
       <c r="B147" t="n">
-        <v>0.3026458024978638</v>
+        <v>0.5537726283073425</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>158</v>
       </c>
       <c r="B148" t="n">
-        <v>0.1404988914728165</v>
+        <v>0.5160236358642578</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>159</v>
       </c>
       <c r="B149" t="n">
-        <v>0.1035856232047081</v>
+        <v>0.5036832094192505</v>
       </c>
     </row>
     <row r="150">
@@ -1629,7 +1629,7 @@
         <v>160</v>
       </c>
       <c r="B150" t="n">
-        <v>0.06484396755695343</v>
+        <v>0.5061534643173218</v>
       </c>
     </row>
     <row r="151">
@@ -1637,7 +1637,7 @@
         <v>161</v>
       </c>
       <c r="B151" t="n">
-        <v>0.04757257923483849</v>
+        <v>0.489800363779068</v>
       </c>
     </row>
     <row r="152">
@@ -1645,7 +1645,7 @@
         <v>162</v>
       </c>
       <c r="B152" t="n">
-        <v>0.07109434902667999</v>
+        <v>0.4767180383205414</v>
       </c>
     </row>
     <row r="153">
@@ -1653,7 +1653,7 @@
         <v>163</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1615986078977585</v>
+        <v>0.4762968122959137</v>
       </c>
     </row>
     <row r="154">
@@ -1661,7 +1661,7 @@
         <v>164</v>
       </c>
       <c r="B154" t="n">
-        <v>0.1305731236934662</v>
+        <v>0.4386705458164215</v>
       </c>
     </row>
     <row r="155">
@@ -1669,7 +1669,7 @@
         <v>165</v>
       </c>
       <c r="B155" t="n">
-        <v>0.1096796318888664</v>
+        <v>0.4190337359905243</v>
       </c>
     </row>
     <row r="156">
@@ -1677,7 +1677,7 @@
         <v>166</v>
       </c>
       <c r="B156" t="n">
-        <v>0.1830336898565292</v>
+        <v>0.4285646080970764</v>
       </c>
     </row>
     <row r="157">
@@ -1685,7 +1685,7 @@
         <v>167</v>
       </c>
       <c r="B157" t="n">
-        <v>0.2142694145441055</v>
+        <v>0.4479109048843384</v>
       </c>
     </row>
     <row r="158">
@@ -1693,7 +1693,7 @@
         <v>168</v>
       </c>
       <c r="B158" t="n">
-        <v>0.2093698531389236</v>
+        <v>0.434744268655777</v>
       </c>
     </row>
     <row r="159">
@@ -1701,7 +1701,7 @@
         <v>169</v>
       </c>
       <c r="B159" t="n">
-        <v>0.2928434908390045</v>
+        <v>0.4784721434116364</v>
       </c>
     </row>
     <row r="160">
@@ -1709,7 +1709,7 @@
         <v>170</v>
       </c>
       <c r="B160" t="n">
-        <v>0.2389265298843384</v>
+        <v>0.4642409086227417</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>171</v>
       </c>
       <c r="B161" t="n">
-        <v>0.2761737108230591</v>
+        <v>0.471393346786499</v>
       </c>
     </row>
     <row r="162">
@@ -1725,7 +1725,7 @@
         <v>172</v>
       </c>
       <c r="B162" t="n">
-        <v>0.2723540365695953</v>
+        <v>0.4825408160686493</v>
       </c>
     </row>
     <row r="163">
@@ -1733,7 +1733,7 @@
         <v>173</v>
       </c>
       <c r="B163" t="n">
-        <v>0.1886361092329025</v>
+        <v>0.4734077453613281</v>
       </c>
     </row>
     <row r="164">
@@ -1741,7 +1741,7 @@
         <v>174</v>
       </c>
       <c r="B164" t="n">
-        <v>0.167068287730217</v>
+        <v>0.4676565825939178</v>
       </c>
     </row>
     <row r="165">
@@ -1749,7 +1749,7 @@
         <v>175</v>
       </c>
       <c r="B165" t="n">
-        <v>0.1812178790569305</v>
+        <v>0.4591414034366608</v>
       </c>
     </row>
     <row r="166">
@@ -1757,7 +1757,7 @@
         <v>176</v>
       </c>
       <c r="B166" t="n">
-        <v>0.1325404644012451</v>
+        <v>0.4331340193748474</v>
       </c>
     </row>
     <row r="167">
@@ -1765,7 +1765,7 @@
         <v>177</v>
       </c>
       <c r="B167" t="n">
-        <v>0.01632403954863548</v>
+        <v>0.4172698855400085</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>178</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.06440459936857224</v>
+        <v>0.3945834040641785</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>179</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.1147155240178108</v>
+        <v>0.3954272866249084</v>
       </c>
     </row>
     <row r="170">
@@ -1789,7 +1789,7 @@
         <v>180</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.1794514209032059</v>
+        <v>0.3954439163208008</v>
       </c>
     </row>
     <row r="171">
@@ -1797,7 +1797,7 @@
         <v>181</v>
       </c>
       <c r="B171" t="n">
-        <v>-0.1582266688346863</v>
+        <v>0.4092100262641907</v>
       </c>
     </row>
     <row r="172">
@@ -1805,7 +1805,7 @@
         <v>182</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.1325563788414001</v>
+        <v>0.4131580591201782</v>
       </c>
     </row>
     <row r="173">
@@ -1813,7 +1813,7 @@
         <v>183</v>
       </c>
       <c r="B173" t="n">
-        <v>-0.05457180365920067</v>
+        <v>0.4257287681102753</v>
       </c>
     </row>
     <row r="174">
@@ -1821,7 +1821,7 @@
         <v>184</v>
       </c>
       <c r="B174" t="n">
-        <v>0.08918941020965576</v>
+        <v>0.4748985171318054</v>
       </c>
     </row>
     <row r="175">
@@ -1829,7 +1829,7 @@
         <v>185</v>
       </c>
       <c r="B175" t="n">
-        <v>0.1596680134534836</v>
+        <v>0.4891857802867889</v>
       </c>
     </row>
     <row r="176">
@@ -1837,7 +1837,7 @@
         <v>186</v>
       </c>
       <c r="B176" t="n">
-        <v>0.2199573367834091</v>
+        <v>0.4973211884498596</v>
       </c>
     </row>
     <row r="177">
@@ -1845,7 +1845,7 @@
         <v>187</v>
       </c>
       <c r="B177" t="n">
-        <v>0.2780439257621765</v>
+        <v>0.4953649044036865</v>
       </c>
     </row>
     <row r="178">
@@ -1853,7 +1853,7 @@
         <v>188</v>
       </c>
       <c r="B178" t="n">
-        <v>0.3071747720241547</v>
+        <v>0.4873361587524414</v>
       </c>
     </row>
     <row r="179">
@@ -1861,7 +1861,7 @@
         <v>189</v>
       </c>
       <c r="B179" t="n">
-        <v>0.2830602824687958</v>
+        <v>0.4846165180206299</v>
       </c>
     </row>
     <row r="180">
@@ -1869,7 +1869,7 @@
         <v>190</v>
       </c>
       <c r="B180" t="n">
-        <v>0.2919197380542755</v>
+        <v>0.4933316111564636</v>
       </c>
     </row>
     <row r="181">
@@ -1877,7 +1877,7 @@
         <v>191</v>
       </c>
       <c r="B181" t="n">
-        <v>0.3294099271297455</v>
+        <v>0.5188546180725098</v>
       </c>
     </row>
     <row r="182">
@@ -1885,7 +1885,7 @@
         <v>192</v>
       </c>
       <c r="B182" t="n">
-        <v>0.1938340216875076</v>
+        <v>0.512653112411499</v>
       </c>
     </row>
     <row r="183">
@@ -1893,7 +1893,7 @@
         <v>193</v>
       </c>
       <c r="B183" t="n">
-        <v>0.08239118754863739</v>
+        <v>0.4939923882484436</v>
       </c>
     </row>
     <row r="184">
@@ -1901,7 +1901,7 @@
         <v>194</v>
       </c>
       <c r="B184" t="n">
-        <v>-0.02190346270799637</v>
+        <v>0.4494394958019257</v>
       </c>
     </row>
     <row r="185">
@@ -1909,7 +1909,7 @@
         <v>195</v>
       </c>
       <c r="B185" t="n">
-        <v>0.07575409859418869</v>
+        <v>0.4670561552047729</v>
       </c>
     </row>
     <row r="186">
@@ -1917,7 +1917,7 @@
         <v>196</v>
       </c>
       <c r="B186" t="n">
-        <v>0.199051633477211</v>
+        <v>0.5121484398841858</v>
       </c>
     </row>
     <row r="187">
@@ -1925,7 +1925,7 @@
         <v>197</v>
       </c>
       <c r="B187" t="n">
-        <v>0.32244473695755</v>
+        <v>0.5398262143135071</v>
       </c>
     </row>
     <row r="188">
@@ -1933,7 +1933,7 @@
         <v>198</v>
       </c>
       <c r="B188" t="n">
-        <v>0.4525936543941498</v>
+        <v>0.5619499683380127</v>
       </c>
     </row>
     <row r="189">
@@ -1941,7 +1941,7 @@
         <v>199</v>
       </c>
       <c r="B189" t="n">
-        <v>0.5200269818305969</v>
+        <v>0.5713760256767273</v>
       </c>
     </row>
     <row r="190">
@@ -1949,7 +1949,7 @@
         <v>200</v>
       </c>
       <c r="B190" t="n">
-        <v>0.5871574282646179</v>
+        <v>0.5722728371620178</v>
       </c>
     </row>
     <row r="191">
@@ -1957,7 +1957,7 @@
         <v>201</v>
       </c>
       <c r="B191" t="n">
-        <v>0.5490489602088928</v>
+        <v>0.5609239935874939</v>
       </c>
     </row>
     <row r="192">
@@ -1965,7 +1965,7 @@
         <v>202</v>
       </c>
       <c r="B192" t="n">
-        <v>0.5197260975837708</v>
+        <v>0.5352979898452759</v>
       </c>
     </row>
     <row r="193">
@@ -1973,7 +1973,7 @@
         <v>203</v>
       </c>
       <c r="B193" t="n">
-        <v>0.5153959393501282</v>
+        <v>0.5212490558624268</v>
       </c>
     </row>
     <row r="194">
@@ -1981,7 +1981,7 @@
         <v>204</v>
       </c>
       <c r="B194" t="n">
-        <v>0.425506979227066</v>
+        <v>0.4947844743728638</v>
       </c>
     </row>
     <row r="195">
@@ -1989,7 +1989,7 @@
         <v>205</v>
       </c>
       <c r="B195" t="n">
-        <v>0.263269305229187</v>
+        <v>0.4807715117931366</v>
       </c>
     </row>
     <row r="196">
@@ -1997,7 +1997,7 @@
         <v>206</v>
       </c>
       <c r="B196" t="n">
-        <v>0.1391455680131912</v>
+        <v>0.450703889131546</v>
       </c>
     </row>
     <row r="197">
@@ -2005,7 +2005,7 @@
         <v>207</v>
       </c>
       <c r="B197" t="n">
-        <v>0.1287083327770233</v>
+        <v>0.4451704025268555</v>
       </c>
     </row>
     <row r="198">
@@ -2013,7 +2013,7 @@
         <v>208</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0842646136879921</v>
+        <v>0.442852109670639</v>
       </c>
     </row>
     <row r="199">
@@ -2021,7 +2021,7 @@
         <v>209</v>
       </c>
       <c r="B199" t="n">
-        <v>0.07882055640220642</v>
+        <v>0.4315923750400543</v>
       </c>
     </row>
     <row r="200">
@@ -2029,7 +2029,7 @@
         <v>210</v>
       </c>
       <c r="B200" t="n">
-        <v>0.01423032861202955</v>
+        <v>0.3951601386070251</v>
       </c>
     </row>
     <row r="201">
@@ -2037,7 +2037,7 @@
         <v>211</v>
       </c>
       <c r="B201" t="n">
-        <v>0.03443742915987968</v>
+        <v>0.3845305442810059</v>
       </c>
     </row>
     <row r="202">
@@ -2045,7 +2045,7 @@
         <v>212</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0823853388428688</v>
+        <v>0.3768411874771118</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>213</v>
       </c>
       <c r="B203" t="n">
-        <v>0.08948854357004166</v>
+        <v>0.364879697561264</v>
       </c>
     </row>
     <row r="204">
@@ -2061,7 +2061,7 @@
         <v>214</v>
       </c>
       <c r="B204" t="n">
-        <v>0.1359593123197556</v>
+        <v>0.3703466355800629</v>
       </c>
     </row>
     <row r="205">
@@ -2069,7 +2069,7 @@
         <v>215</v>
       </c>
       <c r="B205" t="n">
-        <v>0.2160163372755051</v>
+        <v>0.3878483772277832</v>
       </c>
     </row>
     <row r="206">
@@ -2077,7 +2077,7 @@
         <v>216</v>
       </c>
       <c r="B206" t="n">
-        <v>0.218024954199791</v>
+        <v>0.3823780119419098</v>
       </c>
     </row>
     <row r="207">
@@ -2085,7 +2085,7 @@
         <v>217</v>
       </c>
       <c r="B207" t="n">
-        <v>0.1792062968015671</v>
+        <v>0.3873579502105713</v>
       </c>
     </row>
     <row r="208">
@@ -2093,7 +2093,7 @@
         <v>218</v>
       </c>
       <c r="B208" t="n">
-        <v>0.2659330368041992</v>
+        <v>0.4166625738143921</v>
       </c>
     </row>
     <row r="209">
@@ -2101,7 +2101,7 @@
         <v>219</v>
       </c>
       <c r="B209" t="n">
-        <v>0.3944339156150818</v>
+        <v>0.4734345078468323</v>
       </c>
     </row>
     <row r="210">
@@ -2109,7 +2109,7 @@
         <v>220</v>
       </c>
       <c r="B210" t="n">
-        <v>0.3729757368564606</v>
+        <v>0.4847603142261505</v>
       </c>
     </row>
     <row r="211">
@@ -2117,7 +2117,7 @@
         <v>221</v>
       </c>
       <c r="B211" t="n">
-        <v>0.4173357784748077</v>
+        <v>0.5426251292228699</v>
       </c>
     </row>
     <row r="212">
@@ -2125,7 +2125,7 @@
         <v>222</v>
       </c>
       <c r="B212" t="n">
-        <v>0.3297122418880463</v>
+        <v>0.5406312942504883</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>223</v>
       </c>
       <c r="B213" t="n">
-        <v>0.3188877701759338</v>
+        <v>0.5497351288795471</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>224</v>
       </c>
       <c r="B214" t="n">
-        <v>0.2710511684417725</v>
+        <v>0.5348944664001465</v>
       </c>
     </row>
     <row r="215">
@@ -2149,7 +2149,7 @@
         <v>225</v>
       </c>
       <c r="B215" t="n">
-        <v>0.2066997736692429</v>
+        <v>0.496154248714447</v>
       </c>
     </row>
     <row r="216">
@@ -2157,7 +2157,7 @@
         <v>226</v>
       </c>
       <c r="B216" t="n">
-        <v>0.1326340734958649</v>
+        <v>0.4843796193599701</v>
       </c>
     </row>
     <row r="217">
@@ -2165,7 +2165,7 @@
         <v>227</v>
       </c>
       <c r="B217" t="n">
-        <v>0.1064393892884254</v>
+        <v>0.4904337823390961</v>
       </c>
     </row>
     <row r="218">
@@ -2173,7 +2173,7 @@
         <v>228</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.02394130453467369</v>
+        <v>0.447800487279892</v>
       </c>
     </row>
     <row r="219">
@@ -2181,7 +2181,7 @@
         <v>229</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.04411422833800316</v>
+        <v>0.4554925560951233</v>
       </c>
     </row>
     <row r="220">
@@ -2189,7 +2189,7 @@
         <v>230</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.04073281958699226</v>
+        <v>0.4425333142280579</v>
       </c>
     </row>
     <row r="221">
@@ -2197,7 +2197,7 @@
         <v>231</v>
       </c>
       <c r="B221" t="n">
-        <v>0.06304353475570679</v>
+        <v>0.48370161652565</v>
       </c>
     </row>
     <row r="222">
@@ -2205,7 +2205,7 @@
         <v>232</v>
       </c>
       <c r="B222" t="n">
-        <v>0.1326772719621658</v>
+        <v>0.5071179866790771</v>
       </c>
     </row>
     <row r="223">
@@ -2213,7 +2213,7 @@
         <v>233</v>
       </c>
       <c r="B223" t="n">
-        <v>0.1024482697248459</v>
+        <v>0.4890696704387665</v>
       </c>
     </row>
     <row r="224">
@@ -2221,7 +2221,7 @@
         <v>234</v>
       </c>
       <c r="B224" t="n">
-        <v>0.118208535015583</v>
+        <v>0.4853057265281677</v>
       </c>
     </row>
     <row r="225">
@@ -2229,7 +2229,7 @@
         <v>235</v>
       </c>
       <c r="B225" t="n">
-        <v>0.1350360661745071</v>
+        <v>0.4613707661628723</v>
       </c>
     </row>
     <row r="226">
@@ -2237,7 +2237,7 @@
         <v>236</v>
       </c>
       <c r="B226" t="n">
-        <v>0.05957817658782005</v>
+        <v>0.4312510788440704</v>
       </c>
     </row>
     <row r="227">
@@ -2245,7 +2245,7 @@
         <v>237</v>
       </c>
       <c r="B227" t="n">
-        <v>0.02783149853348732</v>
+        <v>0.4109906554222107</v>
       </c>
     </row>
     <row r="228">
@@ -2253,7 +2253,7 @@
         <v>238</v>
       </c>
       <c r="B228" t="n">
-        <v>0.01391998957842588</v>
+        <v>0.3953714072704315</v>
       </c>
     </row>
     <row r="229">
@@ -2261,7 +2261,7 @@
         <v>239</v>
       </c>
       <c r="B229" t="n">
-        <v>0.07143553346395493</v>
+        <v>0.4088504314422607</v>
       </c>
     </row>
     <row r="230">
@@ -2269,7 +2269,7 @@
         <v>240</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.004185550846159458</v>
+        <v>0.404081404209137</v>
       </c>
     </row>
     <row r="231">
@@ -2277,7 +2277,7 @@
         <v>241</v>
       </c>
       <c r="B231" t="n">
-        <v>-0.1272706687450409</v>
+        <v>0.3801513612270355</v>
       </c>
     </row>
     <row r="232">
@@ -2285,7 +2285,7 @@
         <v>242</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.200988233089447</v>
+        <v>0.3558934032917023</v>
       </c>
     </row>
     <row r="233">
@@ -2293,7 +2293,7 @@
         <v>243</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.07155698537826538</v>
+        <v>0.3737157881259918</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>244</v>
       </c>
       <c r="B234" t="n">
-        <v>0.0341457910835743</v>
+        <v>0.3872631192207336</v>
       </c>
     </row>
     <row r="235">
@@ -2309,7 +2309,7 @@
         <v>245</v>
       </c>
       <c r="B235" t="n">
-        <v>0.1780345886945724</v>
+        <v>0.4068440198898315</v>
       </c>
     </row>
     <row r="236">
@@ -2317,7 +2317,7 @@
         <v>246</v>
       </c>
       <c r="B236" t="n">
-        <v>0.2544039785861969</v>
+        <v>0.4256182610988617</v>
       </c>
     </row>
     <row r="237">
@@ -2325,7 +2325,7 @@
         <v>247</v>
       </c>
       <c r="B237" t="n">
-        <v>0.3732389509677887</v>
+        <v>0.4453395903110504</v>
       </c>
     </row>
     <row r="238">
@@ -2333,7 +2333,7 @@
         <v>248</v>
       </c>
       <c r="B238" t="n">
-        <v>0.4280070960521698</v>
+        <v>0.4767603278160095</v>
       </c>
     </row>
     <row r="239">
@@ -2341,7 +2341,7 @@
         <v>249</v>
       </c>
       <c r="B239" t="n">
-        <v>0.4593129754066467</v>
+        <v>0.5074484348297119</v>
       </c>
     </row>
     <row r="240">
@@ -2349,7 +2349,7 @@
         <v>250</v>
       </c>
       <c r="B240" t="n">
-        <v>0.5262715220451355</v>
+        <v>0.5465894341468811</v>
       </c>
     </row>
     <row r="241">
@@ -2357,7 +2357,7 @@
         <v>251</v>
       </c>
       <c r="B241" t="n">
-        <v>0.6910989284515381</v>
+        <v>0.6037334799766541</v>
       </c>
     </row>
     <row r="242">
@@ -2365,7 +2365,7 @@
         <v>252</v>
       </c>
       <c r="B242" t="n">
-        <v>0.8445464968681335</v>
+        <v>0.6572213768959045</v>
       </c>
     </row>
     <row r="243">
@@ -2373,7 +2373,7 @@
         <v>253</v>
       </c>
       <c r="B243" t="n">
-        <v>0.6945981979370117</v>
+        <v>0.6560060381889343</v>
       </c>
     </row>
     <row r="244">
@@ -2381,7 +2381,7 @@
         <v>254</v>
       </c>
       <c r="B244" t="n">
-        <v>0.7877269387245178</v>
+        <v>0.7054314613342285</v>
       </c>
     </row>
     <row r="245">
@@ -2389,7 +2389,7 @@
         <v>255</v>
       </c>
       <c r="B245" t="n">
-        <v>0.88941890001297</v>
+        <v>0.768318772315979</v>
       </c>
     </row>
     <row r="246">
@@ -2397,7 +2397,7 @@
         <v>256</v>
       </c>
       <c r="B246" t="n">
-        <v>0.9323118329048157</v>
+        <v>0.8109285831451416</v>
       </c>
     </row>
     <row r="247">
@@ -2405,7 +2405,7 @@
         <v>257</v>
       </c>
       <c r="B247" t="n">
-        <v>0.9930108189582825</v>
+        <v>0.8434302806854248</v>
       </c>
     </row>
     <row r="248">
@@ -2413,7 +2413,7 @@
         <v>258</v>
       </c>
       <c r="B248" t="n">
-        <v>1.08283257484436</v>
+        <v>0.8761533498764038</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="B249" t="n">
-        <v>1.203049778938293</v>
+        <v>0.9004615545272827</v>
       </c>
     </row>
     <row r="250">
@@ -2429,7 +2429,7 @@
         <v>260</v>
       </c>
       <c r="B250" t="n">
-        <v>1.280115485191345</v>
+        <v>0.9138842225074768</v>
       </c>
     </row>
     <row r="251">
@@ -2437,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="B251" t="n">
-        <v>1.299270391464233</v>
+        <v>0.919277012348175</v>
       </c>
     </row>
     <row r="252">
@@ -2445,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="B252" t="n">
-        <v>1.290146470069885</v>
+        <v>0.9249170422554016</v>
       </c>
     </row>
     <row r="253">
@@ -2453,7 +2453,7 @@
         <v>263</v>
       </c>
       <c r="B253" t="n">
-        <v>1.461400270462036</v>
+        <v>0.9334227442741394</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>264</v>
       </c>
       <c r="B254" t="n">
-        <v>1.474647641181946</v>
+        <v>0.9303324818611145</v>
       </c>
     </row>
     <row r="255">
@@ -2469,7 +2469,7 @@
         <v>265</v>
       </c>
       <c r="B255" t="n">
-        <v>1.164133191108704</v>
+        <v>0.9155481457710266</v>
       </c>
     </row>
     <row r="256">
@@ -2477,7 +2477,7 @@
         <v>266</v>
       </c>
       <c r="B256" t="n">
-        <v>0.892955482006073</v>
+        <v>0.8956629633903503</v>
       </c>
     </row>
     <row r="257">
@@ -2485,7 +2485,7 @@
         <v>267</v>
       </c>
       <c r="B257" t="n">
-        <v>0.6654173135757446</v>
+        <v>0.8788019418716431</v>
       </c>
     </row>
     <row r="258">
@@ -2493,7 +2493,7 @@
         <v>268</v>
       </c>
       <c r="B258" t="n">
-        <v>0.5230143666267395</v>
+        <v>0.8710083961486816</v>
       </c>
     </row>
     <row r="259">
@@ -2501,7 +2501,7 @@
         <v>269</v>
       </c>
       <c r="B259" t="n">
-        <v>0.3183243870735168</v>
+        <v>0.8401935696601868</v>
       </c>
     </row>
     <row r="260">
@@ -2509,7 +2509,7 @@
         <v>270</v>
       </c>
       <c r="B260" t="n">
-        <v>0.2375493943691254</v>
+        <v>0.8053904175758362</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>271</v>
       </c>
       <c r="B261" t="n">
-        <v>0.1102438345551491</v>
+        <v>0.7178481221199036</v>
       </c>
     </row>
     <row r="262">
@@ -2525,7 +2525,7 @@
         <v>272</v>
       </c>
       <c r="B262" t="n">
-        <v>-0.0504826046526432</v>
+        <v>0.5598127841949463</v>
       </c>
     </row>
     <row r="263">
@@ -2533,7 +2533,7 @@
         <v>273</v>
       </c>
       <c r="B263" t="n">
-        <v>-0.2855259776115417</v>
+        <v>0.3519706726074219</v>
       </c>
     </row>
     <row r="264">
@@ -2541,7 +2541,7 @@
         <v>274</v>
       </c>
       <c r="B264" t="n">
-        <v>-0.3920092284679413</v>
+        <v>0.254191666841507</v>
       </c>
     </row>
     <row r="265">
@@ -2549,7 +2549,7 @@
         <v>275</v>
       </c>
       <c r="B265" t="n">
-        <v>-0.4568800628185272</v>
+        <v>0.2075724601745605</v>
       </c>
     </row>
     <row r="266">
@@ -2557,7 +2557,7 @@
         <v>276</v>
       </c>
       <c r="B266" t="n">
-        <v>-0.530231237411499</v>
+        <v>0.1864383816719055</v>
       </c>
     </row>
     <row r="267">
@@ -2565,7 +2565,7 @@
         <v>277</v>
       </c>
       <c r="B267" t="n">
-        <v>-0.6258155703544617</v>
+        <v>0.1816333532333374</v>
       </c>
     </row>
     <row r="268">
@@ -2573,7 +2573,7 @@
         <v>278</v>
       </c>
       <c r="B268" t="n">
-        <v>-0.623418927192688</v>
+        <v>0.1698328107595444</v>
       </c>
     </row>
     <row r="269">
@@ -2581,7 +2581,7 @@
         <v>279</v>
       </c>
       <c r="B269" t="n">
-        <v>-0.6319279074668884</v>
+        <v>0.1661356687545776</v>
       </c>
     </row>
     <row r="270">
@@ -2589,7 +2589,7 @@
         <v>280</v>
       </c>
       <c r="B270" t="n">
-        <v>-0.5313966870307922</v>
+        <v>0.1738491803407669</v>
       </c>
     </row>
     <row r="271">
@@ -2597,7 +2597,7 @@
         <v>281</v>
       </c>
       <c r="B271" t="n">
-        <v>-0.4269697368144989</v>
+        <v>0.1787057816982269</v>
       </c>
     </row>
     <row r="272">
@@ -2605,7 +2605,7 @@
         <v>282</v>
       </c>
       <c r="B272" t="n">
-        <v>-0.3035173714160919</v>
+        <v>0.1778447777032852</v>
       </c>
     </row>
     <row r="273">
@@ -2613,7 +2613,7 @@
         <v>283</v>
       </c>
       <c r="B273" t="n">
-        <v>-0.1590838134288788</v>
+        <v>0.1819037348031998</v>
       </c>
     </row>
     <row r="274">
@@ -2621,7 +2621,7 @@
         <v>284</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.146872952580452</v>
+        <v>0.1810712218284607</v>
       </c>
     </row>
     <row r="275">
@@ -2629,7 +2629,7 @@
         <v>285</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.1840991824865341</v>
+        <v>0.1832603067159653</v>
       </c>
     </row>
     <row r="276">
@@ -2637,7 +2637,7 @@
         <v>286</v>
       </c>
       <c r="B276" t="n">
-        <v>-0.1604585498571396</v>
+        <v>0.1885353773832321</v>
       </c>
     </row>
     <row r="277">
@@ -2645,7 +2645,7 @@
         <v>287</v>
       </c>
       <c r="B277" t="n">
-        <v>-0.06986283510923386</v>
+        <v>0.1997944712638855</v>
       </c>
     </row>
     <row r="278">
@@ -2653,7 +2653,7 @@
         <v>288</v>
       </c>
       <c r="B278" t="n">
-        <v>-0.1034384667873383</v>
+        <v>0.2037507444620132</v>
       </c>
     </row>
     <row r="279">
@@ -2661,7 +2661,7 @@
         <v>289</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.06971248239278793</v>
+        <v>0.2343816757202148</v>
       </c>
     </row>
     <row r="280">
@@ -2669,7 +2669,7 @@
         <v>290</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.201027050614357</v>
+        <v>0.2213969230651855</v>
       </c>
     </row>
     <row r="281">
@@ -2677,7 +2677,7 @@
         <v>291</v>
       </c>
       <c r="B281" t="n">
-        <v>-0.1803691238164902</v>
+        <v>0.2223559319972992</v>
       </c>
     </row>
     <row r="282">
@@ -2685,7 +2685,7 @@
         <v>292</v>
       </c>
       <c r="B282" t="n">
-        <v>-0.1998750418424606</v>
+        <v>0.2148083597421646</v>
       </c>
     </row>
     <row r="283">
@@ -2693,7 +2693,7 @@
         <v>293</v>
       </c>
       <c r="B283" t="n">
-        <v>-0.1414345353841782</v>
+        <v>0.2157991677522659</v>
       </c>
     </row>
     <row r="284">
@@ -2701,7 +2701,7 @@
         <v>294</v>
       </c>
       <c r="B284" t="n">
-        <v>-0.03928599134087563</v>
+        <v>0.2152931839227676</v>
       </c>
     </row>
     <row r="285">
@@ -2709,7 +2709,7 @@
         <v>295</v>
       </c>
       <c r="B285" t="n">
-        <v>0.0975099578499794</v>
+        <v>0.2162855267524719</v>
       </c>
     </row>
     <row r="286">
@@ -2717,7 +2717,7 @@
         <v>296</v>
       </c>
       <c r="B286" t="n">
-        <v>0.03888245299458504</v>
+        <v>0.2164431363344193</v>
       </c>
     </row>
     <row r="287">
@@ -2725,7 +2725,7 @@
         <v>297</v>
       </c>
       <c r="B287" t="n">
-        <v>-0.033757533878088</v>
+        <v>0.2176195830106735</v>
       </c>
     </row>
     <row r="288">
@@ -2733,7 +2733,7 @@
         <v>298</v>
       </c>
       <c r="B288" t="n">
-        <v>-0.05296478793025017</v>
+        <v>0.2214525490999222</v>
       </c>
     </row>
     <row r="289">
@@ -2741,7 +2741,7 @@
         <v>299</v>
       </c>
       <c r="B289" t="n">
-        <v>-0.116360180079937</v>
+        <v>0.2177609652280807</v>
       </c>
     </row>
     <row r="290">
@@ -2749,7 +2749,7 @@
         <v>300</v>
       </c>
       <c r="B290" t="n">
-        <v>-0.1613305956125259</v>
+        <v>0.2107469886541367</v>
       </c>
     </row>
     <row r="291">
@@ -2757,7 +2757,7 @@
         <v>301</v>
       </c>
       <c r="B291" t="n">
-        <v>-0.1346292644739151</v>
+        <v>0.2177405506372452</v>
       </c>
     </row>
     <row r="292">
@@ -2765,7 +2765,7 @@
         <v>302</v>
       </c>
       <c r="B292" t="n">
-        <v>-0.2233798801898956</v>
+        <v>0.2026522606611252</v>
       </c>
     </row>
     <row r="293">
@@ -2773,7 +2773,7 @@
         <v>303</v>
       </c>
       <c r="B293" t="n">
-        <v>-0.170499175786972</v>
+        <v>0.2001847177743912</v>
       </c>
     </row>
     <row r="294">
@@ -2781,7 +2781,7 @@
         <v>304</v>
       </c>
       <c r="B294" t="n">
-        <v>0.01342903356999159</v>
+        <v>0.2216605842113495</v>
       </c>
     </row>
     <row r="295">
@@ -2789,7 +2789,7 @@
         <v>305</v>
       </c>
       <c r="B295" t="n">
-        <v>0.04433327540755272</v>
+        <v>0.2262129336595535</v>
       </c>
     </row>
     <row r="296">
@@ -2797,7 +2797,7 @@
         <v>306</v>
       </c>
       <c r="B296" t="n">
-        <v>0.169332817196846</v>
+        <v>0.2389661520719528</v>
       </c>
     </row>
     <row r="297">
@@ -2805,7 +2805,7 @@
         <v>307</v>
       </c>
       <c r="B297" t="n">
-        <v>0.2218146473169327</v>
+        <v>0.2404700368642807</v>
       </c>
     </row>
     <row r="298">
@@ -2813,7 +2813,7 @@
         <v>308</v>
       </c>
       <c r="B298" t="n">
-        <v>0.1332051306962967</v>
+        <v>0.2439243197441101</v>
       </c>
     </row>
     <row r="299">
@@ -2821,7 +2821,7 @@
         <v>309</v>
       </c>
       <c r="B299" t="n">
-        <v>0.002864352427423</v>
+        <v>0.2408530861139297</v>
       </c>
     </row>
     <row r="300">
@@ -2829,7 +2829,7 @@
         <v>310</v>
       </c>
       <c r="B300" t="n">
-        <v>-0.1115426644682884</v>
+        <v>0.2355716377496719</v>
       </c>
     </row>
     <row r="301">
@@ -2837,7 +2837,7 @@
         <v>311</v>
       </c>
       <c r="B301" t="n">
-        <v>-0.1943102329969406</v>
+        <v>0.2303600460290909</v>
       </c>
     </row>
     <row r="302">
@@ -2845,7 +2845,7 @@
         <v>312</v>
       </c>
       <c r="B302" t="n">
-        <v>-0.3494607210159302</v>
+        <v>0.2176383584737778</v>
       </c>
     </row>
     <row r="303">
@@ -2853,7 +2853,7 @@
         <v>313</v>
       </c>
       <c r="B303" t="n">
-        <v>-0.3487034738063812</v>
+        <v>0.2129802703857422</v>
       </c>
     </row>
     <row r="304">
@@ -2861,7 +2861,7 @@
         <v>314</v>
       </c>
       <c r="B304" t="n">
-        <v>-0.4457339942455292</v>
+        <v>0.1920002549886703</v>
       </c>
     </row>
     <row r="305">
@@ -2869,7 +2869,7 @@
         <v>315</v>
       </c>
       <c r="B305" t="n">
-        <v>-0.2990845739841461</v>
+        <v>0.1946661770343781</v>
       </c>
     </row>
     <row r="306">
@@ -2877,7 +2877,7 @@
         <v>316</v>
       </c>
       <c r="B306" t="n">
-        <v>-0.2337921857833862</v>
+        <v>0.1935523748397827</v>
       </c>
     </row>
     <row r="307">
@@ -2885,7 +2885,7 @@
         <v>317</v>
       </c>
       <c r="B307" t="n">
-        <v>-0.1704197078943253</v>
+        <v>0.1967545300722122</v>
       </c>
     </row>
     <row r="308">
@@ -2893,7 +2893,7 @@
         <v>318</v>
       </c>
       <c r="B308" t="n">
-        <v>-0.03162351623177528</v>
+        <v>0.2003692239522934</v>
       </c>
     </row>
     <row r="309">
@@ -2901,7 +2901,7 @@
         <v>319</v>
       </c>
       <c r="B309" t="n">
-        <v>0.02060812711715698</v>
+        <v>0.2003626674413681</v>
       </c>
     </row>
     <row r="310">
@@ -2909,7 +2909,7 @@
         <v>320</v>
       </c>
       <c r="B310" t="n">
-        <v>0.06157868728041649</v>
+        <v>0.2059076428413391</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>321</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.02825351059436798</v>
+        <v>0.2057446837425232</v>
       </c>
     </row>
     <row r="312">
@@ -2925,7 +2925,7 @@
         <v>322</v>
       </c>
       <c r="B312" t="n">
-        <v>-0.0365709476172924</v>
+        <v>0.2116250544786453</v>
       </c>
     </row>
     <row r="313">
@@ -2933,7 +2933,7 @@
         <v>323</v>
       </c>
       <c r="B313" t="n">
-        <v>-0.08207263797521591</v>
+        <v>0.2147577852010727</v>
       </c>
     </row>
     <row r="314">
@@ -2941,7 +2941,7 @@
         <v>324</v>
       </c>
       <c r="B314" t="n">
-        <v>-0.1786866188049316</v>
+        <v>0.2204886674880981</v>
       </c>
     </row>
     <row r="315">
@@ -2949,7 +2949,7 @@
         <v>325</v>
       </c>
       <c r="B315" t="n">
-        <v>-0.2373645454645157</v>
+        <v>0.2176233977079391</v>
       </c>
     </row>
     <row r="316">
@@ -2957,7 +2957,7 @@
         <v>326</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.3545064628124237</v>
+        <v>0.201641321182251</v>
       </c>
     </row>
     <row r="317">
@@ -2965,7 +2965,7 @@
         <v>327</v>
       </c>
       <c r="B317" t="n">
-        <v>-0.3131364285945892</v>
+        <v>0.1879670321941376</v>
       </c>
     </row>
     <row r="318">
@@ -2973,7 +2973,7 @@
         <v>328</v>
       </c>
       <c r="B318" t="n">
-        <v>-0.2299432754516602</v>
+        <v>0.1909201890230179</v>
       </c>
     </row>
     <row r="319">
@@ -2981,7 +2981,7 @@
         <v>329</v>
       </c>
       <c r="B319" t="n">
-        <v>-0.1110865995287895</v>
+        <v>0.1985002160072327</v>
       </c>
     </row>
     <row r="320">
@@ -2989,7 +2989,7 @@
         <v>330</v>
       </c>
       <c r="B320" t="n">
-        <v>-0.02953150495886803</v>
+        <v>0.1981896311044693</v>
       </c>
     </row>
     <row r="321">
@@ -2997,7 +2997,7 @@
         <v>331</v>
       </c>
       <c r="B321" t="n">
-        <v>0.07795580476522446</v>
+        <v>0.2019226998090744</v>
       </c>
     </row>
     <row r="322">
@@ -3005,7 +3005,7 @@
         <v>332</v>
       </c>
       <c r="B322" t="n">
-        <v>0.1778796166181564</v>
+        <v>0.2048420161008835</v>
       </c>
     </row>
     <row r="323">
@@ -3013,7 +3013,7 @@
         <v>333</v>
       </c>
       <c r="B323" t="n">
-        <v>0.09762971848249435</v>
+        <v>0.2087391018867493</v>
       </c>
     </row>
     <row r="324">
@@ -3021,7 +3021,7 @@
         <v>334</v>
       </c>
       <c r="B324" t="n">
-        <v>0.03804288432002068</v>
+        <v>0.2090571820735931</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>335</v>
       </c>
       <c r="B325" t="n">
-        <v>0.07040436565876007</v>
+        <v>0.2220552712678909</v>
       </c>
     </row>
     <row r="326">
@@ -3037,7 +3037,7 @@
         <v>336</v>
       </c>
       <c r="B326" t="n">
-        <v>-0.03363301977515221</v>
+        <v>0.2240195423364639</v>
       </c>
     </row>
     <row r="327">
@@ -3045,7 +3045,7 @@
         <v>337</v>
       </c>
       <c r="B327" t="n">
-        <v>-0.05717617645859718</v>
+        <v>0.2419421970844269</v>
       </c>
     </row>
     <row r="328">
@@ -3053,7 +3053,7 @@
         <v>338</v>
       </c>
       <c r="B328" t="n">
-        <v>-0.1416530609130859</v>
+        <v>0.2444282174110413</v>
       </c>
     </row>
     <row r="329">
@@ -3061,7 +3061,7 @@
         <v>339</v>
       </c>
       <c r="B329" t="n">
-        <v>-0.06468742340803146</v>
+        <v>0.2473313957452774</v>
       </c>
     </row>
     <row r="330">
@@ -3069,7 +3069,7 @@
         <v>340</v>
       </c>
       <c r="B330" t="n">
-        <v>-0.06932955980300903</v>
+        <v>0.2429914027452469</v>
       </c>
     </row>
     <row r="331">
@@ -3077,7 +3077,7 @@
         <v>341</v>
       </c>
       <c r="B331" t="n">
-        <v>0.03459195792675018</v>
+        <v>0.2484195381402969</v>
       </c>
     </row>
     <row r="332">
@@ -3085,7 +3085,7 @@
         <v>342</v>
       </c>
       <c r="B332" t="n">
-        <v>0.0540272556245327</v>
+        <v>0.2506754398345947</v>
       </c>
     </row>
     <row r="333">
@@ -3093,7 +3093,7 @@
         <v>343</v>
       </c>
       <c r="B333" t="n">
-        <v>0.1354387998580933</v>
+        <v>0.2658710479736328</v>
       </c>
     </row>
     <row r="334">
@@ -3101,7 +3101,7 @@
         <v>344</v>
       </c>
       <c r="B334" t="n">
-        <v>0.13655985891819</v>
+        <v>0.264655202627182</v>
       </c>
     </row>
     <row r="335">
@@ -3109,7 +3109,7 @@
         <v>345</v>
       </c>
       <c r="B335" t="n">
-        <v>0.09226657450199127</v>
+        <v>0.2711520493030548</v>
       </c>
     </row>
     <row r="336">
@@ -3117,7 +3117,7 @@
         <v>346</v>
       </c>
       <c r="B336" t="n">
-        <v>0.1187714338302612</v>
+        <v>0.2898110747337341</v>
       </c>
     </row>
     <row r="337">
@@ -3125,7 +3125,7 @@
         <v>347</v>
       </c>
       <c r="B337" t="n">
-        <v>0.05273003503680229</v>
+        <v>0.2850775420665741</v>
       </c>
     </row>
     <row r="338">
@@ -3133,7 +3133,7 @@
         <v>348</v>
       </c>
       <c r="B338" t="n">
-        <v>-0.002924744971096516</v>
+        <v>0.2851853966712952</v>
       </c>
     </row>
     <row r="339">
@@ -3141,7 +3141,7 @@
         <v>349</v>
       </c>
       <c r="B339" t="n">
-        <v>0.00307058822363615</v>
+        <v>0.2874373197555542</v>
       </c>
     </row>
     <row r="340">
@@ -3149,7 +3149,7 @@
         <v>350</v>
       </c>
       <c r="B340" t="n">
-        <v>0.09916158020496368</v>
+        <v>0.3078785836696625</v>
       </c>
     </row>
     <row r="341">
@@ -3157,7 +3157,7 @@
         <v>351</v>
       </c>
       <c r="B341" t="n">
-        <v>0.2348604053258896</v>
+        <v>0.342849999666214</v>
       </c>
     </row>
     <row r="342">
@@ -3165,7 +3165,7 @@
         <v>352</v>
       </c>
       <c r="B342" t="n">
-        <v>0.3085869252681732</v>
+        <v>0.3694159090518951</v>
       </c>
     </row>
     <row r="343">
@@ -3173,7 +3173,7 @@
         <v>353</v>
       </c>
       <c r="B343" t="n">
-        <v>0.4312286078929901</v>
+        <v>0.4093462526798248</v>
       </c>
     </row>
     <row r="344">
@@ -3181,7 +3181,7 @@
         <v>354</v>
       </c>
       <c r="B344" t="n">
-        <v>0.5536285042762756</v>
+        <v>0.4280045330524445</v>
       </c>
     </row>
     <row r="345">
@@ -3189,7 +3189,7 @@
         <v>355</v>
       </c>
       <c r="B345" t="n">
-        <v>0.5314176082611084</v>
+        <v>0.4034889936447144</v>
       </c>
     </row>
     <row r="346">
@@ -3197,7 +3197,7 @@
         <v>356</v>
       </c>
       <c r="B346" t="n">
-        <v>0.4035594165325165</v>
+        <v>0.3566400110721588</v>
       </c>
     </row>
     <row r="347">
@@ -3205,7 +3205,7 @@
         <v>357</v>
       </c>
       <c r="B347" t="n">
-        <v>0.2984523773193359</v>
+        <v>0.3279789090156555</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>358</v>
       </c>
       <c r="B348" t="n">
-        <v>0.177438497543335</v>
+        <v>0.303826630115509</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>359</v>
       </c>
       <c r="B349" t="n">
-        <v>0.1122806891798973</v>
+        <v>0.3085344731807709</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>360</v>
       </c>
       <c r="B350" t="n">
-        <v>-0.08241011947393417</v>
+        <v>0.2863686978816986</v>
       </c>
     </row>
     <row r="351">
@@ -3237,7 +3237,7 @@
         <v>361</v>
       </c>
       <c r="B351" t="n">
-        <v>-0.1393858343362808</v>
+        <v>0.2908693850040436</v>
       </c>
     </row>
     <row r="352">
@@ -3245,7 +3245,7 @@
         <v>362</v>
       </c>
       <c r="B352" t="n">
-        <v>-0.2353483885526657</v>
+        <v>0.2483209818601608</v>
       </c>
     </row>
     <row r="353">
@@ -3253,7 +3253,7 @@
         <v>363</v>
       </c>
       <c r="B353" t="n">
-        <v>-0.1652504503726959</v>
+        <v>0.2475869506597519</v>
       </c>
     </row>
     <row r="354">
@@ -3261,7 +3261,7 @@
         <v>364</v>
       </c>
       <c r="B354" t="n">
-        <v>-0.07944826781749725</v>
+        <v>0.2506109476089478</v>
       </c>
     </row>
     <row r="355">
@@ -3269,7 +3269,7 @@
         <v>365</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.04931539669632912</v>
+        <v>0.2465453445911407</v>
       </c>
     </row>
     <row r="356">
@@ -3277,7 +3277,7 @@
         <v>366</v>
       </c>
       <c r="B356" t="n">
-        <v>0.01992092281579971</v>
+        <v>0.2403517216444016</v>
       </c>
     </row>
     <row r="357">
@@ -3285,7 +3285,7 @@
         <v>367</v>
       </c>
       <c r="B357" t="n">
-        <v>0.001719827763736248</v>
+        <v>0.233588695526123</v>
       </c>
     </row>
     <row r="358">
@@ -3293,7 +3293,7 @@
         <v>368</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.1016642078757286</v>
+        <v>0.2218108177185059</v>
       </c>
     </row>
     <row r="359">
@@ -3301,7 +3301,7 @@
         <v>369</v>
       </c>
       <c r="B359" t="n">
-        <v>-0.2366799265146255</v>
+        <v>0.2064510583877563</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>370</v>
       </c>
       <c r="B360" t="n">
-        <v>-0.2967728674411774</v>
+        <v>0.1968910843133926</v>
       </c>
     </row>
     <row r="361">
@@ -3317,7 +3317,7 @@
         <v>371</v>
       </c>
       <c r="B361" t="n">
-        <v>-0.3223095834255219</v>
+        <v>0.1872077137231827</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>372</v>
       </c>
       <c r="B362" t="n">
-        <v>-0.3732019066810608</v>
+        <v>0.1839220076799393</v>
       </c>
     </row>
     <row r="363">
@@ -3333,7 +3333,7 @@
         <v>373</v>
       </c>
       <c r="B363" t="n">
-        <v>-0.5363053679466248</v>
+        <v>0.1814235597848892</v>
       </c>
     </row>
     <row r="364">
@@ -3341,7 +3341,7 @@
         <v>374</v>
       </c>
       <c r="B364" t="n">
-        <v>-0.5365995764732361</v>
+        <v>0.1740865260362625</v>
       </c>
     </row>
     <row r="365">
@@ -3349,7 +3349,7 @@
         <v>375</v>
       </c>
       <c r="B365" t="n">
-        <v>-0.4880602061748505</v>
+        <v>0.1683238446712494</v>
       </c>
     </row>
     <row r="366">
@@ -3357,7 +3357,7 @@
         <v>376</v>
       </c>
       <c r="B366" t="n">
-        <v>-0.4376388192176819</v>
+        <v>0.1665979027748108</v>
       </c>
     </row>
     <row r="367">
@@ -3365,7 +3365,7 @@
         <v>377</v>
       </c>
       <c r="B367" t="n">
-        <v>-0.2911607921123505</v>
+        <v>0.1765359491109848</v>
       </c>
     </row>
     <row r="368">
@@ -3373,7 +3373,7 @@
         <v>378</v>
       </c>
       <c r="B368" t="n">
-        <v>-0.2142791301012039</v>
+        <v>0.1768147349357605</v>
       </c>
     </row>
     <row r="369">
@@ -3381,7 +3381,7 @@
         <v>379</v>
       </c>
       <c r="B369" t="n">
-        <v>-0.04287131503224373</v>
+        <v>0.1816005706787109</v>
       </c>
     </row>
     <row r="370">
@@ -3389,7 +3389,7 @@
         <v>380</v>
       </c>
       <c r="B370" t="n">
-        <v>-0.04160832986235619</v>
+        <v>0.1815575808286667</v>
       </c>
     </row>
     <row r="371">
@@ -3397,7 +3397,7 @@
         <v>381</v>
       </c>
       <c r="B371" t="n">
-        <v>-0.06956733018159866</v>
+        <v>0.1836698204278946</v>
       </c>
     </row>
     <row r="372">
@@ -3405,7 +3405,7 @@
         <v>382</v>
       </c>
       <c r="B372" t="n">
-        <v>-0.1569703817367554</v>
+        <v>0.1874957978725433</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>383</v>
       </c>
       <c r="B373" t="n">
-        <v>-0.09879530221223831</v>
+        <v>0.1996719539165497</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>384</v>
       </c>
       <c r="B374" t="n">
-        <v>-0.1008378267288208</v>
+        <v>0.2049160897731781</v>
       </c>
     </row>
     <row r="375">
@@ -3429,7 +3429,7 @@
         <v>385</v>
       </c>
       <c r="B375" t="n">
-        <v>-0.06140723451972008</v>
+        <v>0.2323745787143707</v>
       </c>
     </row>
     <row r="376">
@@ -3437,7 +3437,7 @@
         <v>386</v>
       </c>
       <c r="B376" t="n">
-        <v>-0.0516144298017025</v>
+        <v>0.2384379953145981</v>
       </c>
     </row>
     <row r="377">
@@ -3445,7 +3445,7 @@
         <v>387</v>
       </c>
       <c r="B377" t="n">
-        <v>0.02105864509940147</v>
+        <v>0.2609246969223022</v>
       </c>
     </row>
     <row r="378">
@@ -3453,7 +3453,7 @@
         <v>388</v>
       </c>
       <c r="B378" t="n">
-        <v>0.1423699110746384</v>
+        <v>0.2919764220714569</v>
       </c>
     </row>
     <row r="379">
@@ -3461,7 +3461,7 @@
         <v>389</v>
       </c>
       <c r="B379" t="n">
-        <v>0.2384044378995895</v>
+        <v>0.3191040456295013</v>
       </c>
     </row>
     <row r="380">
@@ -3469,7 +3469,7 @@
         <v>390</v>
       </c>
       <c r="B380" t="n">
-        <v>0.4307401180267334</v>
+        <v>0.3771127164363861</v>
       </c>
     </row>
     <row r="381">
@@ -3477,7 +3477,7 @@
         <v>391</v>
       </c>
       <c r="B381" t="n">
-        <v>0.5821384787559509</v>
+        <v>0.4184023141860962</v>
       </c>
     </row>
     <row r="382">
@@ -3485,7 +3485,7 @@
         <v>392</v>
       </c>
       <c r="B382" t="n">
-        <v>0.621315598487854</v>
+        <v>0.4820243418216705</v>
       </c>
     </row>
     <row r="383">
@@ -3493,7 +3493,7 @@
         <v>393</v>
       </c>
       <c r="B383" t="n">
-        <v>0.5748788118362427</v>
+        <v>0.543533980846405</v>
       </c>
     </row>
     <row r="384">
@@ -3501,7 +3501,7 @@
         <v>394</v>
       </c>
       <c r="B384" t="n">
-        <v>0.5679563283920288</v>
+        <v>0.6694107055664062</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>395</v>
       </c>
       <c r="B385" t="n">
-        <v>0.5928474068641663</v>
+        <v>0.7754206657409668</v>
       </c>
     </row>
     <row r="386">
@@ -3517,7 +3517,7 @@
         <v>396</v>
       </c>
       <c r="B386" t="n">
-        <v>0.4793058931827545</v>
+        <v>0.8175200223922729</v>
       </c>
     </row>
     <row r="387">
@@ -3525,7 +3525,7 @@
         <v>397</v>
       </c>
       <c r="B387" t="n">
-        <v>0.5089794397354126</v>
+        <v>0.8207940459251404</v>
       </c>
     </row>
     <row r="388">
@@ -3533,7 +3533,7 @@
         <v>398</v>
       </c>
       <c r="B388" t="n">
-        <v>0.4242641627788544</v>
+        <v>0.7844116687774658</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>399</v>
       </c>
       <c r="B389" t="n">
-        <v>0.340101569890976</v>
+        <v>0.7410357594490051</v>
       </c>
     </row>
     <row r="390">
@@ -3549,7 +3549,7 @@
         <v>400</v>
       </c>
       <c r="B390" t="n">
-        <v>0.2802316248416901</v>
+        <v>0.7110026478767395</v>
       </c>
     </row>
     <row r="391">
@@ -3557,7 +3557,7 @@
         <v>401</v>
       </c>
       <c r="B391" t="n">
-        <v>0.2008021622896194</v>
+        <v>0.6514527797698975</v>
       </c>
     </row>
     <row r="392">
@@ -3565,7 +3565,7 @@
         <v>402</v>
       </c>
       <c r="B392" t="n">
-        <v>0.1378946006298065</v>
+        <v>0.5915749073028564</v>
       </c>
     </row>
     <row r="393">
@@ -3573,7 +3573,7 @@
         <v>403</v>
       </c>
       <c r="B393" t="n">
-        <v>0.1030592918395996</v>
+        <v>0.5257111191749573</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>404</v>
       </c>
       <c r="B394" t="n">
-        <v>-0.007345681078732014</v>
+        <v>0.4750222861766815</v>
       </c>
     </row>
     <row r="395">
@@ -3589,7 +3589,7 @@
         <v>405</v>
       </c>
       <c r="B395" t="n">
-        <v>-0.1060464009642601</v>
+        <v>0.4211851954460144</v>
       </c>
     </row>
     <row r="396">
@@ -3597,7 +3597,7 @@
         <v>406</v>
       </c>
       <c r="B396" t="n">
-        <v>-0.2002663910388947</v>
+        <v>0.3792272508144379</v>
       </c>
     </row>
     <row r="397">
@@ -3605,7 +3605,7 @@
         <v>407</v>
       </c>
       <c r="B397" t="n">
-        <v>-0.2896014451980591</v>
+        <v>0.3448614478111267</v>
       </c>
     </row>
     <row r="398">
@@ -3613,7 +3613,7 @@
         <v>408</v>
       </c>
       <c r="B398" t="n">
-        <v>-0.3896593153476715</v>
+        <v>0.3350720405578613</v>
       </c>
     </row>
     <row r="399">
@@ -3621,7 +3621,7 @@
         <v>409</v>
       </c>
       <c r="B399" t="n">
-        <v>-0.3661608099937439</v>
+        <v>0.3030035495758057</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>410</v>
       </c>
       <c r="B400" t="n">
-        <v>-0.4315111339092255</v>
+        <v>0.2811274528503418</v>
       </c>
     </row>
     <row r="401">
@@ -3637,7 +3637,7 @@
         <v>411</v>
       </c>
       <c r="B401" t="n">
-        <v>-0.4292566478252411</v>
+        <v>0.2657552361488342</v>
       </c>
     </row>
     <row r="402">
@@ -3645,7 +3645,7 @@
         <v>412</v>
       </c>
       <c r="B402" t="n">
-        <v>-0.4028021991252899</v>
+        <v>0.2575534582138062</v>
       </c>
     </row>
     <row r="403">
@@ -3653,7 +3653,7 @@
         <v>413</v>
       </c>
       <c r="B403" t="n">
-        <v>-0.3328074216842651</v>
+        <v>0.2685704827308655</v>
       </c>
     </row>
     <row r="404">
@@ -3661,7 +3661,7 @@
         <v>414</v>
       </c>
       <c r="B404" t="n">
-        <v>-0.2591399550437927</v>
+        <v>0.2728218734264374</v>
       </c>
     </row>
     <row r="405">
@@ -3669,7 +3669,7 @@
         <v>415</v>
       </c>
       <c r="B405" t="n">
-        <v>-0.1533925086259842</v>
+        <v>0.2903021574020386</v>
       </c>
     </row>
     <row r="406">
@@ -3677,7 +3677,7 @@
         <v>416</v>
       </c>
       <c r="B406" t="n">
-        <v>-0.03548811376094818</v>
+        <v>0.3033324480056763</v>
       </c>
     </row>
     <row r="407">
@@ -3685,7 +3685,7 @@
         <v>417</v>
       </c>
       <c r="B407" t="n">
-        <v>0.03123324736952782</v>
+        <v>0.3284955024719238</v>
       </c>
     </row>
     <row r="408">
@@ -3693,7 +3693,7 @@
         <v>418</v>
       </c>
       <c r="B408" t="n">
-        <v>0.08233267813920975</v>
+        <v>0.350617527961731</v>
       </c>
     </row>
     <row r="409">
@@ -3701,7 +3701,7 @@
         <v>419</v>
       </c>
       <c r="B409" t="n">
-        <v>0.1459556967020035</v>
+        <v>0.3749359250068665</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>420</v>
       </c>
       <c r="B410" t="n">
-        <v>0.07970603555440903</v>
+        <v>0.3705170154571533</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>421</v>
       </c>
       <c r="B411" t="n">
-        <v>-0.007678625173866749</v>
+        <v>0.3923578858375549</v>
       </c>
     </row>
     <row r="412">
@@ -3725,7 +3725,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="n">
-        <v>-0.1205837950110435</v>
+        <v>0.3757527768611908</v>
       </c>
     </row>
     <row r="413">
@@ -3733,7 +3733,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="n">
-        <v>-0.168821394443512</v>
+        <v>0.3778086602687836</v>
       </c>
     </row>
     <row r="414">
@@ -3741,7 +3741,7 @@
         <v>424</v>
       </c>
       <c r="B414" t="n">
-        <v>-0.1885140538215637</v>
+        <v>0.3728928864002228</v>
       </c>
     </row>
     <row r="415">
@@ -3749,7 +3749,7 @@
         <v>425</v>
       </c>
       <c r="B415" t="n">
-        <v>-0.1994047611951828</v>
+        <v>0.3658621609210968</v>
       </c>
     </row>
     <row r="416">
@@ -3757,7 +3757,7 @@
         <v>426</v>
       </c>
       <c r="B416" t="n">
-        <v>-0.2033374607563019</v>
+        <v>0.3536282777786255</v>
       </c>
     </row>
     <row r="417">
@@ -3765,7 +3765,7 @@
         <v>427</v>
       </c>
       <c r="B417" t="n">
-        <v>-0.1934757381677628</v>
+        <v>0.3406117260456085</v>
       </c>
     </row>
     <row r="418">
@@ -3773,7 +3773,7 @@
         <v>428</v>
       </c>
       <c r="B418" t="n">
-        <v>-0.1942801624536514</v>
+        <v>0.3220204710960388</v>
       </c>
     </row>
     <row r="419">
@@ -3781,7 +3781,7 @@
         <v>429</v>
       </c>
       <c r="B419" t="n">
-        <v>-0.1749651432037354</v>
+        <v>0.3170038759708405</v>
       </c>
     </row>
     <row r="420">
@@ -3789,7 +3789,7 @@
         <v>430</v>
       </c>
       <c r="B420" t="n">
-        <v>-0.1446215063333511</v>
+        <v>0.3189200162887573</v>
       </c>
     </row>
     <row r="421">
@@ -3797,7 +3797,7 @@
         <v>431</v>
       </c>
       <c r="B421" t="n">
-        <v>-0.1178292706608772</v>
+        <v>0.327630877494812</v>
       </c>
     </row>
     <row r="422">
@@ -3805,7 +3805,7 @@
         <v>432</v>
       </c>
       <c r="B422" t="n">
-        <v>-0.1276094019412994</v>
+        <v>0.3254889845848083</v>
       </c>
     </row>
     <row r="423">
@@ -3813,7 +3813,7 @@
         <v>433</v>
       </c>
       <c r="B423" t="n">
-        <v>-0.0959523543715477</v>
+        <v>0.3369730114936829</v>
       </c>
     </row>
     <row r="424">
@@ -3821,7 +3821,7 @@
         <v>434</v>
       </c>
       <c r="B424" t="n">
-        <v>-0.1296621412038803</v>
+        <v>0.3396128118038177</v>
       </c>
     </row>
     <row r="425">
@@ -3829,7 +3829,7 @@
         <v>435</v>
       </c>
       <c r="B425" t="n">
-        <v>-0.1156102940440178</v>
+        <v>0.3408511877059937</v>
       </c>
     </row>
     <row r="426">
@@ -3837,7 +3837,7 @@
         <v>436</v>
       </c>
       <c r="B426" t="n">
-        <v>-0.1220740750432014</v>
+        <v>0.3504908084869385</v>
       </c>
     </row>
     <row r="427">
@@ -3845,7 +3845,7 @@
         <v>437</v>
       </c>
       <c r="B427" t="n">
-        <v>-0.1407282054424286</v>
+        <v>0.3522657454013824</v>
       </c>
     </row>
     <row r="428">
@@ -3853,7 +3853,7 @@
         <v>438</v>
       </c>
       <c r="B428" t="n">
-        <v>-0.1503014713525772</v>
+        <v>0.3440901339054108</v>
       </c>
     </row>
     <row r="429">
@@ -3861,7 +3861,7 @@
         <v>439</v>
       </c>
       <c r="B429" t="n">
-        <v>-0.1669248938560486</v>
+        <v>0.3309394419193268</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>440</v>
       </c>
       <c r="B430" t="n">
-        <v>-0.1694000512361526</v>
+        <v>0.3222258388996124</v>
       </c>
     </row>
     <row r="431">
@@ -3877,7 +3877,7 @@
         <v>441</v>
       </c>
       <c r="B431" t="n">
-        <v>-0.197480246424675</v>
+        <v>0.3200969099998474</v>
       </c>
     </row>
     <row r="432">
@@ -3885,7 +3885,7 @@
         <v>442</v>
       </c>
       <c r="B432" t="n">
-        <v>-0.2256836891174316</v>
+        <v>0.3151680827140808</v>
       </c>
     </row>
     <row r="433">
@@ -3893,7 +3893,7 @@
         <v>443</v>
       </c>
       <c r="B433" t="n">
-        <v>-0.2270814627408981</v>
+        <v>0.3250826895236969</v>
       </c>
     </row>
     <row r="434">
@@ -3901,7 +3901,7 @@
         <v>444</v>
       </c>
       <c r="B434" t="n">
-        <v>-0.2626490592956543</v>
+        <v>0.3178144693374634</v>
       </c>
     </row>
     <row r="435">
@@ -3909,7 +3909,7 @@
         <v>445</v>
       </c>
       <c r="B435" t="n">
-        <v>-0.2312148213386536</v>
+        <v>0.3225965797901154</v>
       </c>
     </row>
     <row r="436">
@@ -3917,7 +3917,7 @@
         <v>446</v>
       </c>
       <c r="B436" t="n">
-        <v>-0.209721639752388</v>
+        <v>0.3235957622528076</v>
       </c>
     </row>
     <row r="437">
@@ -3925,7 +3925,7 @@
         <v>447</v>
       </c>
       <c r="B437" t="n">
-        <v>-0.18525430560112</v>
+        <v>0.3310054838657379</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>448</v>
       </c>
       <c r="B438" t="n">
-        <v>-0.1180763468146324</v>
+        <v>0.3482646346092224</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>449</v>
       </c>
       <c r="B439" t="n">
-        <v>-0.09475983679294586</v>
+        <v>0.348827600479126</v>
       </c>
     </row>
     <row r="440">
@@ -3949,7 +3949,7 @@
         <v>450</v>
       </c>
       <c r="B440" t="n">
-        <v>-0.07864973694086075</v>
+        <v>0.3382658362388611</v>
       </c>
     </row>
     <row r="441">
@@ -3957,7 +3957,7 @@
         <v>451</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.05943130329251289</v>
+        <v>0.3279651999473572</v>
       </c>
     </row>
     <row r="442">
@@ -3965,7 +3965,7 @@
         <v>452</v>
       </c>
       <c r="B442" t="n">
-        <v>-0.03448494896292686</v>
+        <v>0.3259759843349457</v>
       </c>
     </row>
     <row r="443">
@@ -3973,7 +3973,7 @@
         <v>453</v>
       </c>
       <c r="B443" t="n">
-        <v>-0.001748216338455677</v>
+        <v>0.3324301540851593</v>
       </c>
     </row>
     <row r="444">
@@ -3981,7 +3981,7 @@
         <v>454</v>
       </c>
       <c r="B444" t="n">
-        <v>0.007161258719861507</v>
+        <v>0.3431769013404846</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>455</v>
       </c>
       <c r="B445" t="n">
-        <v>0.03103247657418251</v>
+        <v>0.3582710921764374</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>456</v>
       </c>
       <c r="B446" t="n">
-        <v>-0.06445163488388062</v>
+        <v>0.3624628186225891</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>457</v>
       </c>
       <c r="B447" t="n">
-        <v>-0.08741124719381332</v>
+        <v>0.3473568856716156</v>
       </c>
     </row>
     <row r="448">
@@ -4013,7 +4013,7 @@
         <v>458</v>
       </c>
       <c r="B448" t="n">
-        <v>-0.1178024932742119</v>
+        <v>0.3269852995872498</v>
       </c>
     </row>
     <row r="449">
@@ -4021,7 +4021,7 @@
         <v>459</v>
       </c>
       <c r="B449" t="n">
-        <v>-0.05688104405999184</v>
+        <v>0.3288522362709045</v>
       </c>
     </row>
     <row r="450">
@@ -4029,7 +4029,7 @@
         <v>460</v>
       </c>
       <c r="B450" t="n">
-        <v>-0.01207317877560854</v>
+        <v>0.339370995759964</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>461</v>
       </c>
       <c r="B451" t="n">
-        <v>0.05560801550745964</v>
+        <v>0.3507790863513947</v>
       </c>
     </row>
     <row r="452">
@@ -4045,7 +4045,7 @@
         <v>462</v>
       </c>
       <c r="B452" t="n">
-        <v>0.1172039583325386</v>
+        <v>0.3429648578166962</v>
       </c>
     </row>
     <row r="453">
@@ -4053,7 +4053,7 @@
         <v>463</v>
       </c>
       <c r="B453" t="n">
-        <v>0.1647337973117828</v>
+        <v>0.3429410457611084</v>
       </c>
     </row>
     <row r="454">
@@ -4061,7 +4061,7 @@
         <v>464</v>
       </c>
       <c r="B454" t="n">
-        <v>0.2100702822208405</v>
+        <v>0.3411647975444794</v>
       </c>
     </row>
     <row r="455">
@@ -4069,7 +4069,7 @@
         <v>465</v>
       </c>
       <c r="B455" t="n">
-        <v>0.2086376696825027</v>
+        <v>0.3404675424098969</v>
       </c>
     </row>
     <row r="456">
@@ -4077,7 +4077,7 @@
         <v>466</v>
       </c>
       <c r="B456" t="n">
-        <v>0.2220960706472397</v>
+        <v>0.3495587110519409</v>
       </c>
     </row>
     <row r="457">
@@ -4085,7 +4085,7 @@
         <v>467</v>
       </c>
       <c r="B457" t="n">
-        <v>0.2066191285848618</v>
+        <v>0.3594481945037842</v>
       </c>
     </row>
     <row r="458">
@@ -4093,7 +4093,7 @@
         <v>468</v>
       </c>
       <c r="B458" t="n">
-        <v>0.1332894265651703</v>
+        <v>0.3545441031455994</v>
       </c>
     </row>
     <row r="459">
@@ -4101,7 +4101,7 @@
         <v>469</v>
       </c>
       <c r="B459" t="n">
-        <v>0.01871886476874352</v>
+        <v>0.3537133038043976</v>
       </c>
     </row>
     <row r="460">
@@ -4109,7 +4109,7 @@
         <v>470</v>
       </c>
       <c r="B460" t="n">
-        <v>-0.08243044465780258</v>
+        <v>0.3474380373954773</v>
       </c>
     </row>
     <row r="461">
@@ -4117,7 +4117,7 @@
         <v>471</v>
       </c>
       <c r="B461" t="n">
-        <v>-0.07088875025510788</v>
+        <v>0.3589800596237183</v>
       </c>
     </row>
     <row r="462">
@@ -4125,7 +4125,7 @@
         <v>472</v>
       </c>
       <c r="B462" t="n">
-        <v>-0.109690360724926</v>
+        <v>0.3530591726303101</v>
       </c>
     </row>
     <row r="463">
@@ -4133,7 +4133,7 @@
         <v>473</v>
       </c>
       <c r="B463" t="n">
-        <v>-0.1054209694266319</v>
+        <v>0.3451458215713501</v>
       </c>
     </row>
     <row r="464">
@@ -4141,7 +4141,7 @@
         <v>474</v>
       </c>
       <c r="B464" t="n">
-        <v>-0.1329232901334763</v>
+        <v>0.3293548226356506</v>
       </c>
     </row>
     <row r="465">
@@ -4149,7 +4149,7 @@
         <v>475</v>
       </c>
       <c r="B465" t="n">
-        <v>-0.1117737367749214</v>
+        <v>0.3242888748645782</v>
       </c>
     </row>
     <row r="466">
@@ -4157,7 +4157,7 @@
         <v>476</v>
       </c>
       <c r="B466" t="n">
-        <v>-0.0756971463561058</v>
+        <v>0.3219243288040161</v>
       </c>
     </row>
     <row r="467">
@@ -4165,7 +4165,7 @@
         <v>477</v>
       </c>
       <c r="B467" t="n">
-        <v>-0.06865408271551132</v>
+        <v>0.3155643939971924</v>
       </c>
     </row>
     <row r="468">
@@ -4173,7 +4173,7 @@
         <v>478</v>
       </c>
       <c r="B468" t="n">
-        <v>-0.06266401708126068</v>
+        <v>0.3127900063991547</v>
       </c>
     </row>
     <row r="469">
@@ -4181,7 +4181,7 @@
         <v>479</v>
       </c>
       <c r="B469" t="n">
-        <v>-0.05611510202288628</v>
+        <v>0.3143626749515533</v>
       </c>
     </row>
     <row r="470">
@@ -4189,7 +4189,7 @@
         <v>480</v>
       </c>
       <c r="B470" t="n">
-        <v>-0.06918381899595261</v>
+        <v>0.3131060004234314</v>
       </c>
     </row>
     <row r="471">
@@ -4197,7 +4197,7 @@
         <v>481</v>
       </c>
       <c r="B471" t="n">
-        <v>-0.08517124503850937</v>
+        <v>0.3191260099411011</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>482</v>
       </c>
       <c r="B472" t="n">
-        <v>-0.05409473553299904</v>
+        <v>0.336496889591217</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>483</v>
       </c>
       <c r="B473" t="n">
-        <v>-0.02935792878270149</v>
+        <v>0.3552286922931671</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>484</v>
       </c>
       <c r="B474" t="n">
-        <v>-0.03078807890415192</v>
+        <v>0.3621737957000732</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>485</v>
       </c>
       <c r="B475" t="n">
-        <v>-0.0286000482738018</v>
+        <v>0.3703499436378479</v>
       </c>
     </row>
     <row r="476">
@@ -4237,7 +4237,7 @@
         <v>486</v>
       </c>
       <c r="B476" t="n">
-        <v>-0.04370773211121559</v>
+        <v>0.3702629804611206</v>
       </c>
     </row>
     <row r="477">
@@ -4245,7 +4245,7 @@
         <v>487</v>
       </c>
       <c r="B477" t="n">
-        <v>-0.0697840079665184</v>
+        <v>0.3523614406585693</v>
       </c>
     </row>
     <row r="478">
@@ -4253,7 +4253,7 @@
         <v>488</v>
       </c>
       <c r="B478" t="n">
-        <v>-0.07833930850028992</v>
+        <v>0.3396529853343964</v>
       </c>
     </row>
     <row r="479">
@@ -4261,7 +4261,7 @@
         <v>489</v>
       </c>
       <c r="B479" t="n">
-        <v>-0.11392592638731</v>
+        <v>0.323682963848114</v>
       </c>
     </row>
     <row r="480">
@@ -4269,7 +4269,7 @@
         <v>490</v>
       </c>
       <c r="B480" t="n">
-        <v>-0.1388555318117142</v>
+        <v>0.3244358599185944</v>
       </c>
     </row>
     <row r="481">
@@ -4277,7 +4277,7 @@
         <v>491</v>
       </c>
       <c r="B481" t="n">
-        <v>-0.1433555036783218</v>
+        <v>0.3318006098270416</v>
       </c>
     </row>
     <row r="482">
@@ -4285,7 +4285,7 @@
         <v>492</v>
       </c>
       <c r="B482" t="n">
-        <v>-0.2049157023429871</v>
+        <v>0.3251309990882874</v>
       </c>
     </row>
     <row r="483">
@@ -4293,7 +4293,7 @@
         <v>493</v>
       </c>
       <c r="B483" t="n">
-        <v>-0.2230748683214188</v>
+        <v>0.3350098431110382</v>
       </c>
     </row>
     <row r="484">
@@ -4301,7 +4301,7 @@
         <v>494</v>
       </c>
       <c r="B484" t="n">
-        <v>-0.2191505581140518</v>
+        <v>0.3290951550006866</v>
       </c>
     </row>
     <row r="485">
@@ -4309,7 +4309,7 @@
         <v>495</v>
       </c>
       <c r="B485" t="n">
-        <v>-0.2078755348920822</v>
+        <v>0.3484632670879364</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>496</v>
       </c>
       <c r="B486" t="n">
-        <v>-0.1864715665578842</v>
+        <v>0.3601029515266418</v>
       </c>
     </row>
     <row r="487">
@@ -4325,7 +4325,7 @@
         <v>497</v>
       </c>
       <c r="B487" t="n">
-        <v>-0.2291861772537231</v>
+        <v>0.3468591570854187</v>
       </c>
     </row>
     <row r="488">
@@ -4333,7 +4333,7 @@
         <v>498</v>
       </c>
       <c r="B488" t="n">
-        <v>-0.2412006407976151</v>
+        <v>0.3356551229953766</v>
       </c>
     </row>
     <row r="489">
@@ -4341,7 +4341,7 @@
         <v>499</v>
       </c>
       <c r="B489" t="n">
-        <v>-0.2482565194368362</v>
+        <v>0.3266296088695526</v>
       </c>
     </row>
     <row r="490">
@@ -4349,7 +4349,7 @@
         <v>500</v>
       </c>
       <c r="B490" t="n">
-        <v>-0.2550293505191803</v>
+        <v>0.3189934194087982</v>
       </c>
     </row>
     <row r="491">
@@ -4357,7 +4357,7 @@
         <v>501</v>
       </c>
       <c r="B491" t="n">
-        <v>-0.2600869238376617</v>
+        <v>0.3113695681095123</v>
       </c>
     </row>
     <row r="492">
@@ -4365,7 +4365,7 @@
         <v>502</v>
       </c>
       <c r="B492" t="n">
-        <v>-0.2469143718481064</v>
+        <v>0.3036713898181915</v>
       </c>
     </row>
     <row r="493">
@@ -4373,7 +4373,7 @@
         <v>503</v>
       </c>
       <c r="B493" t="n">
-        <v>-0.2331409007310867</v>
+        <v>0.304568350315094</v>
       </c>
     </row>
     <row r="494">
@@ -4381,7 +4381,7 @@
         <v>504</v>
       </c>
       <c r="B494" t="n">
-        <v>-0.2681474387645721</v>
+        <v>0.3002641797065735</v>
       </c>
     </row>
     <row r="495">
@@ -4389,7 +4389,7 @@
         <v>505</v>
       </c>
       <c r="B495" t="n">
-        <v>-0.2629301846027374</v>
+        <v>0.2875529229640961</v>
       </c>
     </row>
     <row r="496">
@@ -4397,7 +4397,7 @@
         <v>506</v>
       </c>
       <c r="B496" t="n">
-        <v>-0.2928672730922699</v>
+        <v>0.2713790237903595</v>
       </c>
     </row>
     <row r="497">
@@ -4405,7 +4405,7 @@
         <v>507</v>
       </c>
       <c r="B497" t="n">
-        <v>-0.2150302231311798</v>
+        <v>0.2681928873062134</v>
       </c>
     </row>
     <row r="498">
@@ -4413,7 +4413,7 @@
         <v>508</v>
       </c>
       <c r="B498" t="n">
-        <v>-0.1388345062732697</v>
+        <v>0.2636053860187531</v>
       </c>
     </row>
     <row r="499">
@@ -4421,7 +4421,7 @@
         <v>509</v>
       </c>
       <c r="B499" t="n">
-        <v>-0.08972389250993729</v>
+        <v>0.2640876471996307</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>510</v>
       </c>
       <c r="B500" t="n">
-        <v>-0.02962778136134148</v>
+        <v>0.2686030566692352</v>
       </c>
     </row>
     <row r="501">
@@ -4437,7 +4437,7 @@
         <v>511</v>
       </c>
       <c r="B501" t="n">
-        <v>0.04372772201895714</v>
+        <v>0.2767133712768555</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>512</v>
       </c>
       <c r="B502" t="n">
-        <v>0.09783417731523514</v>
+        <v>0.2962785363197327</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>513</v>
       </c>
       <c r="B503" t="n">
-        <v>0.1569942235946655</v>
+        <v>0.3194253742694855</v>
       </c>
     </row>
     <row r="504">
@@ -4461,7 +4461,7 @@
         <v>514</v>
       </c>
       <c r="B504" t="n">
-        <v>0.2082616835832596</v>
+        <v>0.3458096385002136</v>
       </c>
     </row>
     <row r="505">
@@ -4469,7 +4469,7 @@
         <v>515</v>
       </c>
       <c r="B505" t="n">
-        <v>0.2822918295860291</v>
+        <v>0.3849852085113525</v>
       </c>
     </row>
     <row r="506">
@@ -4477,7 +4477,7 @@
         <v>516</v>
       </c>
       <c r="B506" t="n">
-        <v>0.324894517660141</v>
+        <v>0.4159407615661621</v>
       </c>
     </row>
     <row r="507">
@@ -4485,7 +4485,7 @@
         <v>517</v>
       </c>
       <c r="B507" t="n">
-        <v>0.1821462363004684</v>
+        <v>0.4184573888778687</v>
       </c>
     </row>
     <row r="508">
@@ -4493,7 +4493,7 @@
         <v>518</v>
       </c>
       <c r="B508" t="n">
-        <v>0.2063626497983932</v>
+        <v>0.4577140212059021</v>
       </c>
     </row>
     <row r="509">
@@ -4501,7 +4501,7 @@
         <v>519</v>
       </c>
       <c r="B509" t="n">
-        <v>0.2245970070362091</v>
+        <v>0.4946871101856232</v>
       </c>
     </row>
     <row r="510">
@@ -4509,7 +4509,7 @@
         <v>520</v>
       </c>
       <c r="B510" t="n">
-        <v>0.2877448499202728</v>
+        <v>0.5374352335929871</v>
       </c>
     </row>
     <row r="511">
@@ -4517,7 +4517,7 @@
         <v>521</v>
       </c>
       <c r="B511" t="n">
-        <v>0.3459457159042358</v>
+        <v>0.5822939872741699</v>
       </c>
     </row>
     <row r="512">
@@ -4525,7 +4525,7 @@
         <v>522</v>
       </c>
       <c r="B512" t="n">
-        <v>0.4498279988765717</v>
+        <v>0.63713538646698</v>
       </c>
     </row>
     <row r="513">
@@ -4533,7 +4533,7 @@
         <v>523</v>
       </c>
       <c r="B513" t="n">
-        <v>0.5217812657356262</v>
+        <v>0.6820434331893921</v>
       </c>
     </row>
     <row r="514">
@@ -4541,7 +4541,7 @@
         <v>524</v>
       </c>
       <c r="B514" t="n">
-        <v>0.5801660418510437</v>
+        <v>0.7285361289978027</v>
       </c>
     </row>
     <row r="515">
@@ -4549,7 +4549,7 @@
         <v>525</v>
       </c>
       <c r="B515" t="n">
-        <v>0.6425114870071411</v>
+        <v>0.7677403688430786</v>
       </c>
     </row>
     <row r="516">
@@ -4557,7 +4557,7 @@
         <v>526</v>
       </c>
       <c r="B516" t="n">
-        <v>0.6581228375434875</v>
+        <v>0.8049435019493103</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>527</v>
       </c>
       <c r="B517" t="n">
-        <v>0.7944349050521851</v>
+        <v>0.8523222208023071</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>528</v>
       </c>
       <c r="B518" t="n">
-        <v>0.7797719836235046</v>
+        <v>0.8624336719512939</v>
       </c>
     </row>
   </sheetData>
